--- a/reports/latest/Passed_Test_Cases.xlsx
+++ b/reports/latest/Passed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3550" uniqueCount="1550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3578" uniqueCount="1562">
   <si>
     <t>Test ID</t>
   </si>
@@ -2080,6 +2080,15 @@
     <t>Expected CRUD Operations scenario 23 completes cleanly with status 200 OK.</t>
   </si>
   <si>
+    <t>TC_CRUD_024</t>
+  </si>
+  <si>
+    <t>Verify CRUD Operations Mobile Scenario 24 - Boundary Condition</t>
+  </si>
+  <si>
+    <t>Expected CRUD Operations scenario 24 completes cleanly with status 200 OK.</t>
+  </si>
+  <si>
     <t>TC_CRUD_025</t>
   </si>
   <si>
@@ -2656,6 +2665,15 @@
     <t>Expected Input Validation scenario 7 completes cleanly with status 200 OK.</t>
   </si>
   <si>
+    <t>TC_VAL_008</t>
+  </si>
+  <si>
+    <t>Verify Input Validation Mobile Scenario 8 - Core Path</t>
+  </si>
+  <si>
+    <t>Expected Input Validation scenario 8 completes cleanly with status 200 OK.</t>
+  </si>
+  <si>
     <t>TC_VAL_009</t>
   </si>
   <si>
@@ -3073,6 +3091,15 @@
     <t>Expected Error Handling scenario 14 completes cleanly with status 200 OK.</t>
   </si>
   <si>
+    <t>TC_ERR_015</t>
+  </si>
+  <si>
+    <t>Verify Error Handling Mobile Scenario 15 - Boundary Condition</t>
+  </si>
+  <si>
+    <t>Expected Error Handling scenario 15 completes cleanly with status 200 OK.</t>
+  </si>
+  <si>
     <t>TC_ERR_016</t>
   </si>
   <si>
@@ -3494,6 +3521,15 @@
   </si>
   <si>
     <t>Expected File Upload scenario 1 completes cleanly with status 200 OK.</t>
+  </si>
+  <si>
+    <t>TC_FILE_002</t>
+  </si>
+  <si>
+    <t>Verify File Upload Mobile Scenario 2 - Core Path</t>
+  </si>
+  <si>
+    <t>Expected File Upload scenario 2 completes cleanly with status 200 OK.</t>
   </si>
   <si>
     <t>TC_FILE_003</t>
@@ -5050,7 +5086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H507"/>
+  <dimension ref="A1:H511"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5112,7 +5148,7 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>105</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -5138,7 +5174,7 @@
         <v>14</v>
       </c>
       <c r="H3">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5164,7 +5200,7 @@
         <v>14</v>
       </c>
       <c r="H4">
-        <v>262</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -5190,7 +5226,7 @@
         <v>14</v>
       </c>
       <c r="H5">
-        <v>251</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -5216,7 +5252,7 @@
         <v>14</v>
       </c>
       <c r="H6">
-        <v>161</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -5242,7 +5278,7 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>232</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -5268,7 +5304,7 @@
         <v>14</v>
       </c>
       <c r="H8">
-        <v>260</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -5294,7 +5330,7 @@
         <v>14</v>
       </c>
       <c r="H9">
-        <v>191</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -5320,7 +5356,7 @@
         <v>14</v>
       </c>
       <c r="H10">
-        <v>243</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -5346,7 +5382,7 @@
         <v>14</v>
       </c>
       <c r="H11">
-        <v>103</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -5372,7 +5408,7 @@
         <v>14</v>
       </c>
       <c r="H12">
-        <v>117</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -5398,7 +5434,7 @@
         <v>14</v>
       </c>
       <c r="H13">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -5424,7 +5460,7 @@
         <v>14</v>
       </c>
       <c r="H14">
-        <v>95</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -5450,7 +5486,7 @@
         <v>14</v>
       </c>
       <c r="H15">
-        <v>176</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -5476,7 +5512,7 @@
         <v>14</v>
       </c>
       <c r="H16">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -5502,7 +5538,7 @@
         <v>14</v>
       </c>
       <c r="H17">
-        <v>258</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -5528,7 +5564,7 @@
         <v>14</v>
       </c>
       <c r="H18">
-        <v>175</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -5554,7 +5590,7 @@
         <v>14</v>
       </c>
       <c r="H19">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -5580,7 +5616,7 @@
         <v>14</v>
       </c>
       <c r="H20">
-        <v>171</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -5606,7 +5642,7 @@
         <v>14</v>
       </c>
       <c r="H21">
-        <v>130</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -5632,7 +5668,7 @@
         <v>14</v>
       </c>
       <c r="H22">
-        <v>173</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -5658,7 +5694,7 @@
         <v>14</v>
       </c>
       <c r="H23">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -5684,7 +5720,7 @@
         <v>14</v>
       </c>
       <c r="H24">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -5710,7 +5746,7 @@
         <v>14</v>
       </c>
       <c r="H25">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -5736,7 +5772,7 @@
         <v>14</v>
       </c>
       <c r="H26">
-        <v>217</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -5762,7 +5798,7 @@
         <v>14</v>
       </c>
       <c r="H27">
-        <v>183</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -5788,7 +5824,7 @@
         <v>14</v>
       </c>
       <c r="H28">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -5814,7 +5850,7 @@
         <v>14</v>
       </c>
       <c r="H29">
-        <v>180</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -5840,7 +5876,7 @@
         <v>14</v>
       </c>
       <c r="H30">
-        <v>246</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -5866,7 +5902,7 @@
         <v>14</v>
       </c>
       <c r="H31">
-        <v>183</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -5892,7 +5928,7 @@
         <v>14</v>
       </c>
       <c r="H32">
-        <v>215</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -5918,7 +5954,7 @@
         <v>14</v>
       </c>
       <c r="H33">
-        <v>180</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -5944,7 +5980,7 @@
         <v>14</v>
       </c>
       <c r="H34">
-        <v>191</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -5970,7 +6006,7 @@
         <v>14</v>
       </c>
       <c r="H35">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -5996,7 +6032,7 @@
         <v>14</v>
       </c>
       <c r="H36">
-        <v>254</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -6022,7 +6058,7 @@
         <v>14</v>
       </c>
       <c r="H37">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -6048,7 +6084,7 @@
         <v>14</v>
       </c>
       <c r="H38">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -6074,7 +6110,7 @@
         <v>14</v>
       </c>
       <c r="H39">
-        <v>198</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -6100,7 +6136,7 @@
         <v>14</v>
       </c>
       <c r="H40">
-        <v>163</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -6126,7 +6162,7 @@
         <v>14</v>
       </c>
       <c r="H41">
-        <v>194</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6152,7 +6188,7 @@
         <v>14</v>
       </c>
       <c r="H42">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -6178,7 +6214,7 @@
         <v>14</v>
       </c>
       <c r="H43">
-        <v>170</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -6204,7 +6240,7 @@
         <v>14</v>
       </c>
       <c r="H44">
-        <v>259</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -6230,7 +6266,7 @@
         <v>14</v>
       </c>
       <c r="H45">
-        <v>153</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -6256,7 +6292,7 @@
         <v>14</v>
       </c>
       <c r="H46">
-        <v>98</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -6282,7 +6318,7 @@
         <v>14</v>
       </c>
       <c r="H47">
-        <v>165</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -6308,7 +6344,7 @@
         <v>14</v>
       </c>
       <c r="H48">
-        <v>134</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -6334,7 +6370,7 @@
         <v>14</v>
       </c>
       <c r="H49">
-        <v>163</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -6360,7 +6396,7 @@
         <v>14</v>
       </c>
       <c r="H50">
-        <v>212</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -6386,7 +6422,7 @@
         <v>14</v>
       </c>
       <c r="H51">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -6412,7 +6448,7 @@
         <v>14</v>
       </c>
       <c r="H52">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -6438,7 +6474,7 @@
         <v>14</v>
       </c>
       <c r="H53">
-        <v>93</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -6464,7 +6500,7 @@
         <v>14</v>
       </c>
       <c r="H54">
-        <v>154</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -6490,7 +6526,7 @@
         <v>14</v>
       </c>
       <c r="H55">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -6516,7 +6552,7 @@
         <v>14</v>
       </c>
       <c r="H56">
-        <v>210</v>
+        <v>255</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -6542,7 +6578,7 @@
         <v>14</v>
       </c>
       <c r="H57">
-        <v>170</v>
+        <v>262</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -6568,7 +6604,7 @@
         <v>14</v>
       </c>
       <c r="H58">
-        <v>251</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -6594,7 +6630,7 @@
         <v>14</v>
       </c>
       <c r="H59">
-        <v>200</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -6620,7 +6656,7 @@
         <v>14</v>
       </c>
       <c r="H60">
-        <v>219</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -6646,7 +6682,7 @@
         <v>14</v>
       </c>
       <c r="H61">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -6672,7 +6708,7 @@
         <v>14</v>
       </c>
       <c r="H62">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -6698,7 +6734,7 @@
         <v>14</v>
       </c>
       <c r="H63">
-        <v>156</v>
+        <v>263</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -6724,7 +6760,7 @@
         <v>14</v>
       </c>
       <c r="H64">
-        <v>108</v>
+        <v>248</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -6750,7 +6786,7 @@
         <v>14</v>
       </c>
       <c r="H65">
-        <v>98</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -6776,7 +6812,7 @@
         <v>14</v>
       </c>
       <c r="H66">
-        <v>264</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -6802,7 +6838,7 @@
         <v>14</v>
       </c>
       <c r="H67">
-        <v>152</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -6828,7 +6864,7 @@
         <v>14</v>
       </c>
       <c r="H68">
-        <v>108</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -6854,7 +6890,7 @@
         <v>14</v>
       </c>
       <c r="H69">
-        <v>106</v>
+        <v>255</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -6880,7 +6916,7 @@
         <v>14</v>
       </c>
       <c r="H70">
-        <v>257</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -6906,7 +6942,7 @@
         <v>14</v>
       </c>
       <c r="H71">
-        <v>138</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -6932,7 +6968,7 @@
         <v>14</v>
       </c>
       <c r="H72">
-        <v>227</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -6958,7 +6994,7 @@
         <v>14</v>
       </c>
       <c r="H73">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -6984,7 +7020,7 @@
         <v>14</v>
       </c>
       <c r="H74">
-        <v>100</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -7010,7 +7046,7 @@
         <v>14</v>
       </c>
       <c r="H75">
-        <v>191</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -7036,7 +7072,7 @@
         <v>14</v>
       </c>
       <c r="H76">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -7062,7 +7098,7 @@
         <v>14</v>
       </c>
       <c r="H77">
-        <v>170</v>
+        <v>241</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -7088,7 +7124,7 @@
         <v>14</v>
       </c>
       <c r="H78">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -7114,7 +7150,7 @@
         <v>14</v>
       </c>
       <c r="H79">
-        <v>223</v>
+        <v>249</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -7140,7 +7176,7 @@
         <v>14</v>
       </c>
       <c r="H80">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -7166,7 +7202,7 @@
         <v>14</v>
       </c>
       <c r="H81">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -7192,7 +7228,7 @@
         <v>14</v>
       </c>
       <c r="H82">
-        <v>100</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -7218,7 +7254,7 @@
         <v>14</v>
       </c>
       <c r="H83">
-        <v>259</v>
+        <v>232</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -7244,7 +7280,7 @@
         <v>14</v>
       </c>
       <c r="H84">
-        <v>209</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -7270,7 +7306,7 @@
         <v>14</v>
       </c>
       <c r="H85">
-        <v>150</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -7296,7 +7332,7 @@
         <v>14</v>
       </c>
       <c r="H86">
-        <v>242</v>
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -7322,7 +7358,7 @@
         <v>14</v>
       </c>
       <c r="H87">
-        <v>139</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -7348,7 +7384,7 @@
         <v>14</v>
       </c>
       <c r="H88">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -7374,7 +7410,7 @@
         <v>14</v>
       </c>
       <c r="H89">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -7400,7 +7436,7 @@
         <v>14</v>
       </c>
       <c r="H90">
-        <v>114</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -7426,7 +7462,7 @@
         <v>14</v>
       </c>
       <c r="H91">
-        <v>163</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -7452,7 +7488,7 @@
         <v>14</v>
       </c>
       <c r="H92">
-        <v>244</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -7478,7 +7514,7 @@
         <v>14</v>
       </c>
       <c r="H93">
-        <v>218</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -7504,7 +7540,7 @@
         <v>14</v>
       </c>
       <c r="H94">
-        <v>255</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -7530,7 +7566,7 @@
         <v>14</v>
       </c>
       <c r="H95">
-        <v>166</v>
+        <v>180</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -7556,7 +7592,7 @@
         <v>14</v>
       </c>
       <c r="H96">
-        <v>230</v>
+        <v>216</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -7582,7 +7618,7 @@
         <v>14</v>
       </c>
       <c r="H97">
-        <v>254</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -7608,7 +7644,7 @@
         <v>14</v>
       </c>
       <c r="H98">
-        <v>260</v>
+        <v>153</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -7634,7 +7670,7 @@
         <v>14</v>
       </c>
       <c r="H99">
-        <v>212</v>
+        <v>180</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -7660,7 +7696,7 @@
         <v>14</v>
       </c>
       <c r="H100">
-        <v>178</v>
+        <v>268</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -7686,7 +7722,7 @@
         <v>14</v>
       </c>
       <c r="H101">
-        <v>245</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -7712,7 +7748,7 @@
         <v>14</v>
       </c>
       <c r="H102">
-        <v>118</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -7738,7 +7774,7 @@
         <v>14</v>
       </c>
       <c r="H103">
-        <v>171</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -7764,7 +7800,7 @@
         <v>14</v>
       </c>
       <c r="H104">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -7790,7 +7826,7 @@
         <v>14</v>
       </c>
       <c r="H105">
-        <v>93</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -7816,7 +7852,7 @@
         <v>14</v>
       </c>
       <c r="H106">
-        <v>101</v>
+        <v>195</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -7842,7 +7878,7 @@
         <v>14</v>
       </c>
       <c r="H107">
-        <v>133</v>
+        <v>220</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -7868,7 +7904,7 @@
         <v>14</v>
       </c>
       <c r="H108">
-        <v>152</v>
+        <v>180</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -7894,7 +7930,7 @@
         <v>14</v>
       </c>
       <c r="H109">
-        <v>98</v>
+        <v>134</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -7920,7 +7956,7 @@
         <v>14</v>
       </c>
       <c r="H110">
-        <v>247</v>
+        <v>126</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -7946,7 +7982,7 @@
         <v>14</v>
       </c>
       <c r="H111">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -7972,7 +8008,7 @@
         <v>14</v>
       </c>
       <c r="H112">
-        <v>124</v>
+        <v>196</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -7998,7 +8034,7 @@
         <v>14</v>
       </c>
       <c r="H113">
-        <v>125</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -8024,7 +8060,7 @@
         <v>14</v>
       </c>
       <c r="H114">
-        <v>161</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -8050,7 +8086,7 @@
         <v>14</v>
       </c>
       <c r="H115">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -8076,7 +8112,7 @@
         <v>14</v>
       </c>
       <c r="H116">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -8102,7 +8138,7 @@
         <v>14</v>
       </c>
       <c r="H117">
-        <v>96</v>
+        <v>166</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -8128,7 +8164,7 @@
         <v>14</v>
       </c>
       <c r="H118">
-        <v>136</v>
+        <v>246</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -8154,7 +8190,7 @@
         <v>14</v>
       </c>
       <c r="H119">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -8180,7 +8216,7 @@
         <v>14</v>
       </c>
       <c r="H120">
-        <v>147</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -8206,7 +8242,7 @@
         <v>14</v>
       </c>
       <c r="H121">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -8232,7 +8268,7 @@
         <v>14</v>
       </c>
       <c r="H122">
-        <v>243</v>
+        <v>128</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -8258,7 +8294,7 @@
         <v>14</v>
       </c>
       <c r="H123">
-        <v>112</v>
+        <v>214</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -8284,7 +8320,7 @@
         <v>14</v>
       </c>
       <c r="H124">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -8310,7 +8346,7 @@
         <v>14</v>
       </c>
       <c r="H125">
-        <v>241</v>
+        <v>163</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -8336,7 +8372,7 @@
         <v>14</v>
       </c>
       <c r="H126">
-        <v>254</v>
+        <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -8362,7 +8398,7 @@
         <v>14</v>
       </c>
       <c r="H127">
-        <v>156</v>
+        <v>124</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -8388,7 +8424,7 @@
         <v>14</v>
       </c>
       <c r="H128">
-        <v>222</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -8414,7 +8450,7 @@
         <v>14</v>
       </c>
       <c r="H129">
-        <v>121</v>
+        <v>266</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -8440,7 +8476,7 @@
         <v>14</v>
       </c>
       <c r="H130">
-        <v>218</v>
+        <v>149</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -8466,7 +8502,7 @@
         <v>14</v>
       </c>
       <c r="H131">
-        <v>215</v>
+        <v>94</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -8492,7 +8528,7 @@
         <v>14</v>
       </c>
       <c r="H132">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -8518,7 +8554,7 @@
         <v>14</v>
       </c>
       <c r="H133">
-        <v>258</v>
+        <v>98</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -8544,7 +8580,7 @@
         <v>14</v>
       </c>
       <c r="H134">
-        <v>190</v>
+        <v>119</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -8570,7 +8606,7 @@
         <v>14</v>
       </c>
       <c r="H135">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -8596,7 +8632,7 @@
         <v>14</v>
       </c>
       <c r="H136">
-        <v>265</v>
+        <v>138</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -8622,7 +8658,7 @@
         <v>14</v>
       </c>
       <c r="H137">
-        <v>204</v>
+        <v>254</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -8648,7 +8684,7 @@
         <v>14</v>
       </c>
       <c r="H138">
-        <v>173</v>
+        <v>113</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -8674,7 +8710,7 @@
         <v>14</v>
       </c>
       <c r="H139">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -8700,7 +8736,7 @@
         <v>14</v>
       </c>
       <c r="H140">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -8726,7 +8762,7 @@
         <v>14</v>
       </c>
       <c r="H141">
-        <v>211</v>
+        <v>136</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -8752,7 +8788,7 @@
         <v>14</v>
       </c>
       <c r="H142">
-        <v>130</v>
+        <v>170</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -8778,7 +8814,7 @@
         <v>14</v>
       </c>
       <c r="H143">
-        <v>166</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -8804,7 +8840,7 @@
         <v>14</v>
       </c>
       <c r="H144">
-        <v>214</v>
+        <v>133</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -8830,7 +8866,7 @@
         <v>14</v>
       </c>
       <c r="H145">
-        <v>103</v>
+        <v>174</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -8856,7 +8892,7 @@
         <v>14</v>
       </c>
       <c r="H146">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -8882,7 +8918,7 @@
         <v>14</v>
       </c>
       <c r="H147">
-        <v>203</v>
+        <v>186</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -8908,7 +8944,7 @@
         <v>14</v>
       </c>
       <c r="H148">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -8934,7 +8970,7 @@
         <v>14</v>
       </c>
       <c r="H149">
-        <v>147</v>
+        <v>231</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -8960,7 +8996,7 @@
         <v>14</v>
       </c>
       <c r="H150">
-        <v>109</v>
+        <v>214</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -8986,7 +9022,7 @@
         <v>14</v>
       </c>
       <c r="H151">
-        <v>104</v>
+        <v>182</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -9012,7 +9048,7 @@
         <v>14</v>
       </c>
       <c r="H152">
-        <v>166</v>
+        <v>134</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -9038,7 +9074,7 @@
         <v>14</v>
       </c>
       <c r="H153">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -9064,7 +9100,7 @@
         <v>14</v>
       </c>
       <c r="H154">
-        <v>110</v>
+        <v>219</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -9090,7 +9126,7 @@
         <v>14</v>
       </c>
       <c r="H155">
-        <v>118</v>
+        <v>220</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -9116,7 +9152,7 @@
         <v>14</v>
       </c>
       <c r="H156">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -9142,7 +9178,7 @@
         <v>14</v>
       </c>
       <c r="H157">
-        <v>177</v>
+        <v>105</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -9168,7 +9204,7 @@
         <v>14</v>
       </c>
       <c r="H158">
-        <v>126</v>
+        <v>238</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -9194,7 +9230,7 @@
         <v>14</v>
       </c>
       <c r="H159">
-        <v>199</v>
+        <v>238</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -9220,7 +9256,7 @@
         <v>14</v>
       </c>
       <c r="H160">
-        <v>252</v>
+        <v>195</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -9246,7 +9282,7 @@
         <v>14</v>
       </c>
       <c r="H161">
-        <v>219</v>
+        <v>113</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -9272,7 +9308,7 @@
         <v>14</v>
       </c>
       <c r="H162">
-        <v>147</v>
+        <v>181</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -9298,7 +9334,7 @@
         <v>14</v>
       </c>
       <c r="H163">
-        <v>266</v>
+        <v>144</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -9324,7 +9360,7 @@
         <v>14</v>
       </c>
       <c r="H164">
-        <v>228</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -9350,7 +9386,7 @@
         <v>14</v>
       </c>
       <c r="H165">
-        <v>227</v>
+        <v>265</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -9376,7 +9412,7 @@
         <v>14</v>
       </c>
       <c r="H166">
-        <v>194</v>
+        <v>156</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -9402,7 +9438,7 @@
         <v>14</v>
       </c>
       <c r="H167">
-        <v>95</v>
+        <v>226</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -9428,7 +9464,7 @@
         <v>14</v>
       </c>
       <c r="H168">
-        <v>174</v>
+        <v>245</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -9454,7 +9490,7 @@
         <v>14</v>
       </c>
       <c r="H169">
-        <v>166</v>
+        <v>91</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -9480,7 +9516,7 @@
         <v>14</v>
       </c>
       <c r="H170">
-        <v>215</v>
+        <v>155</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -9506,7 +9542,7 @@
         <v>14</v>
       </c>
       <c r="H171">
-        <v>227</v>
+        <v>112</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -9532,7 +9568,7 @@
         <v>14</v>
       </c>
       <c r="H172">
-        <v>216</v>
+        <v>268</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -9558,7 +9594,7 @@
         <v>14</v>
       </c>
       <c r="H173">
-        <v>183</v>
+        <v>208</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -9584,7 +9620,7 @@
         <v>14</v>
       </c>
       <c r="H174">
-        <v>102</v>
+        <v>121</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -9610,7 +9646,7 @@
         <v>14</v>
       </c>
       <c r="H175">
-        <v>159</v>
+        <v>215</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -9636,7 +9672,7 @@
         <v>14</v>
       </c>
       <c r="H176">
-        <v>198</v>
+        <v>244</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -9662,7 +9698,7 @@
         <v>14</v>
       </c>
       <c r="H177">
-        <v>181</v>
+        <v>133</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -9688,7 +9724,7 @@
         <v>14</v>
       </c>
       <c r="H178">
-        <v>99</v>
+        <v>176</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -9714,7 +9750,7 @@
         <v>14</v>
       </c>
       <c r="H179">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -9740,7 +9776,7 @@
         <v>14</v>
       </c>
       <c r="H180">
-        <v>255</v>
+        <v>117</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -9766,7 +9802,7 @@
         <v>14</v>
       </c>
       <c r="H181">
-        <v>156</v>
+        <v>264</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -9792,7 +9828,7 @@
         <v>14</v>
       </c>
       <c r="H182">
-        <v>183</v>
+        <v>164</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -9818,7 +9854,7 @@
         <v>14</v>
       </c>
       <c r="H183">
-        <v>260</v>
+        <v>172</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -9844,7 +9880,7 @@
         <v>14</v>
       </c>
       <c r="H184">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -9870,7 +9906,7 @@
         <v>14</v>
       </c>
       <c r="H185">
-        <v>122</v>
+        <v>91</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -9896,7 +9932,7 @@
         <v>14</v>
       </c>
       <c r="H186">
-        <v>240</v>
+        <v>252</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -9922,7 +9958,7 @@
         <v>14</v>
       </c>
       <c r="H187">
-        <v>229</v>
+        <v>199</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -9948,7 +9984,7 @@
         <v>14</v>
       </c>
       <c r="H188">
-        <v>104</v>
+        <v>213</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -9974,7 +10010,7 @@
         <v>14</v>
       </c>
       <c r="H189">
-        <v>160</v>
+        <v>196</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -10000,7 +10036,7 @@
         <v>14</v>
       </c>
       <c r="H190">
-        <v>255</v>
+        <v>216</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -10026,7 +10062,7 @@
         <v>14</v>
       </c>
       <c r="H191">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -10052,7 +10088,7 @@
         <v>14</v>
       </c>
       <c r="H192">
-        <v>92</v>
+        <v>157</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -10078,7 +10114,7 @@
         <v>14</v>
       </c>
       <c r="H193">
-        <v>267</v>
+        <v>206</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -10104,7 +10140,7 @@
         <v>14</v>
       </c>
       <c r="H194">
-        <v>245</v>
+        <v>113</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -10130,7 +10166,7 @@
         <v>14</v>
       </c>
       <c r="H195">
-        <v>143</v>
+        <v>267</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -10156,7 +10192,7 @@
         <v>14</v>
       </c>
       <c r="H196">
-        <v>201</v>
+        <v>152</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -10182,7 +10218,7 @@
         <v>14</v>
       </c>
       <c r="H197">
-        <v>95</v>
+        <v>259</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -10208,7 +10244,7 @@
         <v>14</v>
       </c>
       <c r="H198">
-        <v>149</v>
+        <v>232</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -10234,7 +10270,7 @@
         <v>14</v>
       </c>
       <c r="H199">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -10260,7 +10296,7 @@
         <v>14</v>
       </c>
       <c r="H200">
-        <v>231</v>
+        <v>169</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -10286,7 +10322,7 @@
         <v>14</v>
       </c>
       <c r="H201">
-        <v>93</v>
+        <v>210</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -10312,7 +10348,7 @@
         <v>14</v>
       </c>
       <c r="H202">
-        <v>233</v>
+        <v>163</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -10338,7 +10374,7 @@
         <v>14</v>
       </c>
       <c r="H203">
-        <v>233</v>
+        <v>166</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -10364,7 +10400,7 @@
         <v>14</v>
       </c>
       <c r="H204">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -10390,7 +10426,7 @@
         <v>14</v>
       </c>
       <c r="H205">
-        <v>190</v>
+        <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -10416,7 +10452,7 @@
         <v>14</v>
       </c>
       <c r="H206">
-        <v>266</v>
+        <v>106</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -10442,7 +10478,7 @@
         <v>14</v>
       </c>
       <c r="H207">
-        <v>90</v>
+        <v>268</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -10468,7 +10504,7 @@
         <v>14</v>
       </c>
       <c r="H208">
-        <v>127</v>
+        <v>222</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -10494,7 +10530,7 @@
         <v>14</v>
       </c>
       <c r="H209">
-        <v>182</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -10520,7 +10556,7 @@
         <v>14</v>
       </c>
       <c r="H210">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -10546,7 +10582,7 @@
         <v>14</v>
       </c>
       <c r="H211">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -10572,7 +10608,7 @@
         <v>14</v>
       </c>
       <c r="H212">
-        <v>228</v>
+        <v>263</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -10598,7 +10634,7 @@
         <v>14</v>
       </c>
       <c r="H213">
-        <v>247</v>
+        <v>223</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -10624,7 +10660,7 @@
         <v>14</v>
       </c>
       <c r="H214">
-        <v>258</v>
+        <v>121</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -10650,7 +10686,7 @@
         <v>14</v>
       </c>
       <c r="H215">
-        <v>179</v>
+        <v>125</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -10676,7 +10712,7 @@
         <v>14</v>
       </c>
       <c r="H216">
-        <v>178</v>
+        <v>211</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -10702,7 +10738,7 @@
         <v>14</v>
       </c>
       <c r="H217">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -10728,7 +10764,7 @@
         <v>14</v>
       </c>
       <c r="H218">
-        <v>190</v>
+        <v>99</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -10754,7 +10790,7 @@
         <v>14</v>
       </c>
       <c r="H219">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
@@ -10780,7 +10816,7 @@
         <v>14</v>
       </c>
       <c r="H220">
-        <v>174</v>
+        <v>224</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -10806,7 +10842,7 @@
         <v>14</v>
       </c>
       <c r="H221">
-        <v>93</v>
+        <v>188</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -10832,7 +10868,7 @@
         <v>14</v>
       </c>
       <c r="H222">
-        <v>106</v>
+        <v>207</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -10858,7 +10894,7 @@
         <v>14</v>
       </c>
       <c r="H223">
-        <v>148</v>
+        <v>126</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
@@ -10884,7 +10920,7 @@
         <v>14</v>
       </c>
       <c r="H224">
-        <v>225</v>
+        <v>121</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
@@ -10910,7 +10946,7 @@
         <v>14</v>
       </c>
       <c r="H225">
-        <v>269</v>
+        <v>226</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -10936,7 +10972,7 @@
         <v>14</v>
       </c>
       <c r="H226">
-        <v>166</v>
+        <v>149</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
@@ -10962,7 +10998,7 @@
         <v>14</v>
       </c>
       <c r="H227">
-        <v>210</v>
+        <v>131</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -10988,7 +11024,7 @@
         <v>14</v>
       </c>
       <c r="H228">
-        <v>224</v>
+        <v>94</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -11014,7 +11050,7 @@
         <v>14</v>
       </c>
       <c r="H229">
-        <v>155</v>
+        <v>181</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
@@ -11040,7 +11076,7 @@
         <v>14</v>
       </c>
       <c r="H230">
-        <v>222</v>
+        <v>145</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
@@ -11066,7 +11102,7 @@
         <v>14</v>
       </c>
       <c r="H231">
-        <v>194</v>
+        <v>155</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
@@ -11092,7 +11128,7 @@
         <v>14</v>
       </c>
       <c r="H232">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
@@ -11118,7 +11154,7 @@
         <v>14</v>
       </c>
       <c r="H233">
-        <v>219</v>
+        <v>178</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
@@ -11144,7 +11180,7 @@
         <v>14</v>
       </c>
       <c r="H234">
-        <v>133</v>
+        <v>222</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
@@ -11170,7 +11206,7 @@
         <v>14</v>
       </c>
       <c r="H235">
-        <v>133</v>
+        <v>90</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
@@ -11196,7 +11232,7 @@
         <v>14</v>
       </c>
       <c r="H236">
-        <v>135</v>
+        <v>112</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
@@ -11222,7 +11258,7 @@
         <v>14</v>
       </c>
       <c r="H237">
-        <v>130</v>
+        <v>236</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
@@ -11248,7 +11284,7 @@
         <v>14</v>
       </c>
       <c r="H238">
-        <v>154</v>
+        <v>94</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
@@ -11274,7 +11310,7 @@
         <v>14</v>
       </c>
       <c r="H239">
-        <v>97</v>
+        <v>191</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
@@ -11300,7 +11336,7 @@
         <v>14</v>
       </c>
       <c r="H240">
-        <v>263</v>
+        <v>159</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
@@ -11308,33 +11344,33 @@
         <v>737</v>
       </c>
       <c r="B241" t="s">
+        <v>620</v>
+      </c>
+      <c r="C241" t="s">
         <v>738</v>
       </c>
-      <c r="C241" t="s">
+      <c r="D241" t="s">
+        <v>50</v>
+      </c>
+      <c r="E241" t="s">
+        <v>12</v>
+      </c>
+      <c r="F241" t="s">
         <v>739</v>
       </c>
-      <c r="D241" t="s">
-        <v>11</v>
-      </c>
-      <c r="E241" t="s">
-        <v>12</v>
-      </c>
-      <c r="F241" t="s">
-        <v>740</v>
-      </c>
       <c r="G241" t="s">
         <v>14</v>
       </c>
       <c r="H241">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>740</v>
+      </c>
+      <c r="B242" t="s">
         <v>741</v>
-      </c>
-      <c r="B242" t="s">
-        <v>738</v>
       </c>
       <c r="C242" t="s">
         <v>742</v>
@@ -11352,7 +11388,7 @@
         <v>14</v>
       </c>
       <c r="H242">
-        <v>123</v>
+        <v>241</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
@@ -11360,7 +11396,7 @@
         <v>744</v>
       </c>
       <c r="B243" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C243" t="s">
         <v>745</v>
@@ -11378,7 +11414,7 @@
         <v>14</v>
       </c>
       <c r="H243">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
@@ -11386,7 +11422,7 @@
         <v>747</v>
       </c>
       <c r="B244" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C244" t="s">
         <v>748</v>
@@ -11404,7 +11440,7 @@
         <v>14</v>
       </c>
       <c r="H244">
-        <v>208</v>
+        <v>244</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
@@ -11412,7 +11448,7 @@
         <v>750</v>
       </c>
       <c r="B245" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C245" t="s">
         <v>751</v>
@@ -11430,7 +11466,7 @@
         <v>14</v>
       </c>
       <c r="H245">
-        <v>204</v>
+        <v>240</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
@@ -11438,7 +11474,7 @@
         <v>753</v>
       </c>
       <c r="B246" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C246" t="s">
         <v>754</v>
@@ -11456,7 +11492,7 @@
         <v>14</v>
       </c>
       <c r="H246">
-        <v>152</v>
+        <v>170</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
@@ -11464,13 +11500,13 @@
         <v>756</v>
       </c>
       <c r="B247" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C247" t="s">
         <v>757</v>
       </c>
       <c r="D247" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E247" t="s">
         <v>12</v>
@@ -11482,7 +11518,7 @@
         <v>14</v>
       </c>
       <c r="H247">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
@@ -11490,7 +11526,7 @@
         <v>759</v>
       </c>
       <c r="B248" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C248" t="s">
         <v>760</v>
@@ -11508,7 +11544,7 @@
         <v>14</v>
       </c>
       <c r="H248">
-        <v>231</v>
+        <v>116</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
@@ -11516,7 +11552,7 @@
         <v>762</v>
       </c>
       <c r="B249" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C249" t="s">
         <v>763</v>
@@ -11534,7 +11570,7 @@
         <v>14</v>
       </c>
       <c r="H249">
-        <v>155</v>
+        <v>186</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
@@ -11542,7 +11578,7 @@
         <v>765</v>
       </c>
       <c r="B250" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C250" t="s">
         <v>766</v>
@@ -11560,7 +11596,7 @@
         <v>14</v>
       </c>
       <c r="H250">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
@@ -11568,7 +11604,7 @@
         <v>768</v>
       </c>
       <c r="B251" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C251" t="s">
         <v>769</v>
@@ -11586,7 +11622,7 @@
         <v>14</v>
       </c>
       <c r="H251">
-        <v>143</v>
+        <v>260</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
@@ -11594,7 +11630,7 @@
         <v>771</v>
       </c>
       <c r="B252" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C252" t="s">
         <v>772</v>
@@ -11612,7 +11648,7 @@
         <v>14</v>
       </c>
       <c r="H252">
-        <v>243</v>
+        <v>267</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
@@ -11620,7 +11656,7 @@
         <v>774</v>
       </c>
       <c r="B253" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C253" t="s">
         <v>775</v>
@@ -11638,7 +11674,7 @@
         <v>14</v>
       </c>
       <c r="H253">
-        <v>120</v>
+        <v>167</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
@@ -11646,7 +11682,7 @@
         <v>777</v>
       </c>
       <c r="B254" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C254" t="s">
         <v>778</v>
@@ -11664,7 +11700,7 @@
         <v>14</v>
       </c>
       <c r="H254">
-        <v>241</v>
+        <v>203</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
@@ -11672,7 +11708,7 @@
         <v>780</v>
       </c>
       <c r="B255" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C255" t="s">
         <v>781</v>
@@ -11690,7 +11726,7 @@
         <v>14</v>
       </c>
       <c r="H255">
-        <v>204</v>
+        <v>114</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
@@ -11698,7 +11734,7 @@
         <v>783</v>
       </c>
       <c r="B256" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C256" t="s">
         <v>784</v>
@@ -11716,7 +11752,7 @@
         <v>14</v>
       </c>
       <c r="H256">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
@@ -11724,7 +11760,7 @@
         <v>786</v>
       </c>
       <c r="B257" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C257" t="s">
         <v>787</v>
@@ -11742,7 +11778,7 @@
         <v>14</v>
       </c>
       <c r="H257">
-        <v>247</v>
+        <v>157</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
@@ -11750,7 +11786,7 @@
         <v>789</v>
       </c>
       <c r="B258" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C258" t="s">
         <v>790</v>
@@ -11768,7 +11804,7 @@
         <v>14</v>
       </c>
       <c r="H258">
-        <v>155</v>
+        <v>204</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
@@ -11776,7 +11812,7 @@
         <v>792</v>
       </c>
       <c r="B259" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C259" t="s">
         <v>793</v>
@@ -11794,7 +11830,7 @@
         <v>14</v>
       </c>
       <c r="H259">
-        <v>256</v>
+        <v>170</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
@@ -11802,7 +11838,7 @@
         <v>795</v>
       </c>
       <c r="B260" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C260" t="s">
         <v>796</v>
@@ -11820,7 +11856,7 @@
         <v>14</v>
       </c>
       <c r="H260">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
@@ -11828,33 +11864,33 @@
         <v>798</v>
       </c>
       <c r="B261" t="s">
+        <v>741</v>
+      </c>
+      <c r="C261" t="s">
         <v>799</v>
       </c>
-      <c r="C261" t="s">
+      <c r="D261" t="s">
+        <v>50</v>
+      </c>
+      <c r="E261" t="s">
+        <v>12</v>
+      </c>
+      <c r="F261" t="s">
         <v>800</v>
       </c>
-      <c r="D261" t="s">
-        <v>11</v>
-      </c>
-      <c r="E261" t="s">
-        <v>12</v>
-      </c>
-      <c r="F261" t="s">
-        <v>801</v>
-      </c>
       <c r="G261" t="s">
         <v>14</v>
       </c>
       <c r="H261">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>801</v>
+      </c>
+      <c r="B262" t="s">
         <v>802</v>
-      </c>
-      <c r="B262" t="s">
-        <v>799</v>
       </c>
       <c r="C262" t="s">
         <v>803</v>
@@ -11872,7 +11908,7 @@
         <v>14</v>
       </c>
       <c r="H262">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
@@ -11880,7 +11916,7 @@
         <v>805</v>
       </c>
       <c r="B263" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C263" t="s">
         <v>806</v>
@@ -11898,7 +11934,7 @@
         <v>14</v>
       </c>
       <c r="H263">
-        <v>161</v>
+        <v>205</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
@@ -11906,7 +11942,7 @@
         <v>808</v>
       </c>
       <c r="B264" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C264" t="s">
         <v>809</v>
@@ -11924,7 +11960,7 @@
         <v>14</v>
       </c>
       <c r="H264">
-        <v>127</v>
+        <v>172</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
@@ -11932,7 +11968,7 @@
         <v>811</v>
       </c>
       <c r="B265" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C265" t="s">
         <v>812</v>
@@ -11950,7 +11986,7 @@
         <v>14</v>
       </c>
       <c r="H265">
-        <v>105</v>
+        <v>252</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
@@ -11958,7 +11994,7 @@
         <v>814</v>
       </c>
       <c r="B266" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C266" t="s">
         <v>815</v>
@@ -11976,7 +12012,7 @@
         <v>14</v>
       </c>
       <c r="H266">
-        <v>102</v>
+        <v>234</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
@@ -11984,13 +12020,13 @@
         <v>817</v>
       </c>
       <c r="B267" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C267" t="s">
         <v>818</v>
       </c>
       <c r="D267" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E267" t="s">
         <v>12</v>
@@ -12002,7 +12038,7 @@
         <v>14</v>
       </c>
       <c r="H267">
-        <v>259</v>
+        <v>208</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
@@ -12010,7 +12046,7 @@
         <v>820</v>
       </c>
       <c r="B268" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C268" t="s">
         <v>821</v>
@@ -12028,7 +12064,7 @@
         <v>14</v>
       </c>
       <c r="H268">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
@@ -12036,7 +12072,7 @@
         <v>823</v>
       </c>
       <c r="B269" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C269" t="s">
         <v>824</v>
@@ -12054,7 +12090,7 @@
         <v>14</v>
       </c>
       <c r="H269">
-        <v>129</v>
+        <v>173</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
@@ -12062,7 +12098,7 @@
         <v>826</v>
       </c>
       <c r="B270" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C270" t="s">
         <v>827</v>
@@ -12080,7 +12116,7 @@
         <v>14</v>
       </c>
       <c r="H270">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -12088,7 +12124,7 @@
         <v>829</v>
       </c>
       <c r="B271" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C271" t="s">
         <v>830</v>
@@ -12106,7 +12142,7 @@
         <v>14</v>
       </c>
       <c r="H271">
-        <v>206</v>
+        <v>257</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
@@ -12114,7 +12150,7 @@
         <v>832</v>
       </c>
       <c r="B272" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C272" t="s">
         <v>833</v>
@@ -12132,7 +12168,7 @@
         <v>14</v>
       </c>
       <c r="H272">
-        <v>253</v>
+        <v>130</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
@@ -12140,7 +12176,7 @@
         <v>835</v>
       </c>
       <c r="B273" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C273" t="s">
         <v>836</v>
@@ -12158,7 +12194,7 @@
         <v>14</v>
       </c>
       <c r="H273">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
@@ -12166,7 +12202,7 @@
         <v>838</v>
       </c>
       <c r="B274" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C274" t="s">
         <v>839</v>
@@ -12184,7 +12220,7 @@
         <v>14</v>
       </c>
       <c r="H274">
-        <v>232</v>
+        <v>191</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
@@ -12192,7 +12228,7 @@
         <v>841</v>
       </c>
       <c r="B275" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C275" t="s">
         <v>842</v>
@@ -12210,7 +12246,7 @@
         <v>14</v>
       </c>
       <c r="H275">
-        <v>235</v>
+        <v>253</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
@@ -12218,7 +12254,7 @@
         <v>844</v>
       </c>
       <c r="B276" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C276" t="s">
         <v>845</v>
@@ -12236,7 +12272,7 @@
         <v>14</v>
       </c>
       <c r="H276">
-        <v>247</v>
+        <v>176</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
@@ -12244,7 +12280,7 @@
         <v>847</v>
       </c>
       <c r="B277" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C277" t="s">
         <v>848</v>
@@ -12262,7 +12298,7 @@
         <v>14</v>
       </c>
       <c r="H277">
-        <v>235</v>
+        <v>164</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
@@ -12270,7 +12306,7 @@
         <v>850</v>
       </c>
       <c r="B278" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C278" t="s">
         <v>851</v>
@@ -12288,7 +12324,7 @@
         <v>14</v>
       </c>
       <c r="H278">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
@@ -12296,7 +12332,7 @@
         <v>853</v>
       </c>
       <c r="B279" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C279" t="s">
         <v>854</v>
@@ -12314,7 +12350,7 @@
         <v>14</v>
       </c>
       <c r="H279">
-        <v>229</v>
+        <v>245</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
@@ -12322,7 +12358,7 @@
         <v>856</v>
       </c>
       <c r="B280" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C280" t="s">
         <v>857</v>
@@ -12340,7 +12376,7 @@
         <v>14</v>
       </c>
       <c r="H280">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
@@ -12348,33 +12384,33 @@
         <v>859</v>
       </c>
       <c r="B281" t="s">
+        <v>802</v>
+      </c>
+      <c r="C281" t="s">
         <v>860</v>
       </c>
-      <c r="C281" t="s">
+      <c r="D281" t="s">
+        <v>50</v>
+      </c>
+      <c r="E281" t="s">
+        <v>12</v>
+      </c>
+      <c r="F281" t="s">
         <v>861</v>
       </c>
-      <c r="D281" t="s">
-        <v>11</v>
-      </c>
-      <c r="E281" t="s">
-        <v>12</v>
-      </c>
-      <c r="F281" t="s">
-        <v>862</v>
-      </c>
       <c r="G281" t="s">
         <v>14</v>
       </c>
       <c r="H281">
-        <v>264</v>
+        <v>137</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>862</v>
+      </c>
+      <c r="B282" t="s">
         <v>863</v>
-      </c>
-      <c r="B282" t="s">
-        <v>860</v>
       </c>
       <c r="C282" t="s">
         <v>864</v>
@@ -12392,7 +12428,7 @@
         <v>14</v>
       </c>
       <c r="H282">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
@@ -12400,7 +12436,7 @@
         <v>866</v>
       </c>
       <c r="B283" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C283" t="s">
         <v>867</v>
@@ -12418,7 +12454,7 @@
         <v>14</v>
       </c>
       <c r="H283">
-        <v>130</v>
+        <v>253</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
@@ -12426,7 +12462,7 @@
         <v>869</v>
       </c>
       <c r="B284" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C284" t="s">
         <v>870</v>
@@ -12444,7 +12480,7 @@
         <v>14</v>
       </c>
       <c r="H284">
-        <v>182</v>
+        <v>122</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
@@ -12452,7 +12488,7 @@
         <v>872</v>
       </c>
       <c r="B285" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C285" t="s">
         <v>873</v>
@@ -12470,7 +12506,7 @@
         <v>14</v>
       </c>
       <c r="H285">
-        <v>241</v>
+        <v>177</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
@@ -12478,7 +12514,7 @@
         <v>875</v>
       </c>
       <c r="B286" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C286" t="s">
         <v>876</v>
@@ -12496,7 +12532,7 @@
         <v>14</v>
       </c>
       <c r="H286">
-        <v>157</v>
+        <v>181</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
@@ -12504,7 +12540,7 @@
         <v>878</v>
       </c>
       <c r="B287" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C287" t="s">
         <v>879</v>
@@ -12522,7 +12558,7 @@
         <v>14</v>
       </c>
       <c r="H287">
-        <v>94</v>
+        <v>210</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
@@ -12530,7 +12566,7 @@
         <v>881</v>
       </c>
       <c r="B288" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C288" t="s">
         <v>882</v>
@@ -12548,7 +12584,7 @@
         <v>14</v>
       </c>
       <c r="H288">
-        <v>102</v>
+        <v>183</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
@@ -12556,7 +12592,7 @@
         <v>884</v>
       </c>
       <c r="B289" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C289" t="s">
         <v>885</v>
@@ -12574,7 +12610,7 @@
         <v>14</v>
       </c>
       <c r="H289">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
@@ -12582,7 +12618,7 @@
         <v>887</v>
       </c>
       <c r="B290" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C290" t="s">
         <v>888</v>
@@ -12600,7 +12636,7 @@
         <v>14</v>
       </c>
       <c r="H290">
-        <v>231</v>
+        <v>199</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
@@ -12608,7 +12644,7 @@
         <v>890</v>
       </c>
       <c r="B291" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C291" t="s">
         <v>891</v>
@@ -12626,7 +12662,7 @@
         <v>14</v>
       </c>
       <c r="H291">
-        <v>252</v>
+        <v>98</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
@@ -12634,13 +12670,13 @@
         <v>893</v>
       </c>
       <c r="B292" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C292" t="s">
         <v>894</v>
       </c>
       <c r="D292" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E292" t="s">
         <v>12</v>
@@ -12652,7 +12688,7 @@
         <v>14</v>
       </c>
       <c r="H292">
-        <v>252</v>
+        <v>101</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
@@ -12660,13 +12696,13 @@
         <v>896</v>
       </c>
       <c r="B293" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C293" t="s">
         <v>897</v>
       </c>
       <c r="D293" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E293" t="s">
         <v>12</v>
@@ -12678,7 +12714,7 @@
         <v>14</v>
       </c>
       <c r="H293">
-        <v>245</v>
+        <v>140</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
@@ -12686,7 +12722,7 @@
         <v>899</v>
       </c>
       <c r="B294" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C294" t="s">
         <v>900</v>
@@ -12704,7 +12740,7 @@
         <v>14</v>
       </c>
       <c r="H294">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
@@ -12712,7 +12748,7 @@
         <v>902</v>
       </c>
       <c r="B295" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C295" t="s">
         <v>903</v>
@@ -12730,7 +12766,7 @@
         <v>14</v>
       </c>
       <c r="H295">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
@@ -12738,7 +12774,7 @@
         <v>905</v>
       </c>
       <c r="B296" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C296" t="s">
         <v>906</v>
@@ -12756,7 +12792,7 @@
         <v>14</v>
       </c>
       <c r="H296">
-        <v>199</v>
+        <v>94</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
@@ -12764,7 +12800,7 @@
         <v>908</v>
       </c>
       <c r="B297" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C297" t="s">
         <v>909</v>
@@ -12782,7 +12818,7 @@
         <v>14</v>
       </c>
       <c r="H297">
-        <v>133</v>
+        <v>246</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
@@ -12790,7 +12826,7 @@
         <v>911</v>
       </c>
       <c r="B298" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C298" t="s">
         <v>912</v>
@@ -12808,7 +12844,7 @@
         <v>14</v>
       </c>
       <c r="H298">
-        <v>231</v>
+        <v>142</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
@@ -12816,7 +12852,7 @@
         <v>914</v>
       </c>
       <c r="B299" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C299" t="s">
         <v>915</v>
@@ -12834,7 +12870,7 @@
         <v>14</v>
       </c>
       <c r="H299">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
@@ -12842,7 +12878,7 @@
         <v>917</v>
       </c>
       <c r="B300" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C300" t="s">
         <v>918</v>
@@ -12860,7 +12896,7 @@
         <v>14</v>
       </c>
       <c r="H300">
-        <v>110</v>
+        <v>245</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
@@ -12868,7 +12904,7 @@
         <v>920</v>
       </c>
       <c r="B301" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C301" t="s">
         <v>921</v>
@@ -12886,7 +12922,7 @@
         <v>14</v>
       </c>
       <c r="H301">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
@@ -12894,7 +12930,7 @@
         <v>923</v>
       </c>
       <c r="B302" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C302" t="s">
         <v>924</v>
@@ -12912,7 +12948,7 @@
         <v>14</v>
       </c>
       <c r="H302">
-        <v>141</v>
+        <v>231</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
@@ -12920,7 +12956,7 @@
         <v>926</v>
       </c>
       <c r="B303" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C303" t="s">
         <v>927</v>
@@ -12938,7 +12974,7 @@
         <v>14</v>
       </c>
       <c r="H303">
-        <v>219</v>
+        <v>202</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
@@ -12946,7 +12982,7 @@
         <v>929</v>
       </c>
       <c r="B304" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C304" t="s">
         <v>930</v>
@@ -12964,7 +13000,7 @@
         <v>14</v>
       </c>
       <c r="H304">
-        <v>107</v>
+        <v>133</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
@@ -12972,7 +13008,7 @@
         <v>932</v>
       </c>
       <c r="B305" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C305" t="s">
         <v>933</v>
@@ -12990,7 +13026,7 @@
         <v>14</v>
       </c>
       <c r="H305">
-        <v>239</v>
+        <v>153</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
@@ -12998,7 +13034,7 @@
         <v>935</v>
       </c>
       <c r="B306" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C306" t="s">
         <v>936</v>
@@ -13016,7 +13052,7 @@
         <v>14</v>
       </c>
       <c r="H306">
-        <v>187</v>
+        <v>246</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
@@ -13024,7 +13060,7 @@
         <v>938</v>
       </c>
       <c r="B307" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C307" t="s">
         <v>939</v>
@@ -13042,7 +13078,7 @@
         <v>14</v>
       </c>
       <c r="H307">
-        <v>242</v>
+        <v>96</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
@@ -13050,7 +13086,7 @@
         <v>941</v>
       </c>
       <c r="B308" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C308" t="s">
         <v>942</v>
@@ -13068,7 +13104,7 @@
         <v>14</v>
       </c>
       <c r="H308">
-        <v>138</v>
+        <v>238</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
@@ -13076,7 +13112,7 @@
         <v>944</v>
       </c>
       <c r="B309" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C309" t="s">
         <v>945</v>
@@ -13094,7 +13130,7 @@
         <v>14</v>
       </c>
       <c r="H309">
-        <v>191</v>
+        <v>140</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
@@ -13102,7 +13138,7 @@
         <v>947</v>
       </c>
       <c r="B310" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C310" t="s">
         <v>948</v>
@@ -13120,7 +13156,7 @@
         <v>14</v>
       </c>
       <c r="H310">
-        <v>200</v>
+        <v>244</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
@@ -13128,7 +13164,7 @@
         <v>950</v>
       </c>
       <c r="B311" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C311" t="s">
         <v>951</v>
@@ -13146,7 +13182,7 @@
         <v>14</v>
       </c>
       <c r="H311">
-        <v>145</v>
+        <v>173</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
@@ -13154,7 +13190,7 @@
         <v>953</v>
       </c>
       <c r="B312" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C312" t="s">
         <v>954</v>
@@ -13172,7 +13208,7 @@
         <v>14</v>
       </c>
       <c r="H312">
-        <v>182</v>
+        <v>139</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
@@ -13180,7 +13216,7 @@
         <v>956</v>
       </c>
       <c r="B313" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C313" t="s">
         <v>957</v>
@@ -13198,7 +13234,7 @@
         <v>14</v>
       </c>
       <c r="H313">
-        <v>186</v>
+        <v>235</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
@@ -13206,7 +13242,7 @@
         <v>959</v>
       </c>
       <c r="B314" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C314" t="s">
         <v>960</v>
@@ -13224,7 +13260,7 @@
         <v>14</v>
       </c>
       <c r="H314">
-        <v>187</v>
+        <v>219</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
@@ -13232,7 +13268,7 @@
         <v>962</v>
       </c>
       <c r="B315" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C315" t="s">
         <v>963</v>
@@ -13250,7 +13286,7 @@
         <v>14</v>
       </c>
       <c r="H315">
-        <v>180</v>
+        <v>263</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
@@ -13258,7 +13294,7 @@
         <v>965</v>
       </c>
       <c r="B316" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C316" t="s">
         <v>966</v>
@@ -13276,7 +13312,7 @@
         <v>14</v>
       </c>
       <c r="H316">
-        <v>174</v>
+        <v>97</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
@@ -13284,7 +13320,7 @@
         <v>968</v>
       </c>
       <c r="B317" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C317" t="s">
         <v>969</v>
@@ -13302,7 +13338,7 @@
         <v>14</v>
       </c>
       <c r="H317">
-        <v>91</v>
+        <v>266</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
@@ -13310,7 +13346,7 @@
         <v>971</v>
       </c>
       <c r="B318" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C318" t="s">
         <v>972</v>
@@ -13328,7 +13364,7 @@
         <v>14</v>
       </c>
       <c r="H318">
-        <v>202</v>
+        <v>239</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
@@ -13336,7 +13372,7 @@
         <v>974</v>
       </c>
       <c r="B319" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C319" t="s">
         <v>975</v>
@@ -13354,7 +13390,7 @@
         <v>14</v>
       </c>
       <c r="H319">
-        <v>195</v>
+        <v>106</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
@@ -13362,59 +13398,59 @@
         <v>977</v>
       </c>
       <c r="B320" t="s">
+        <v>863</v>
+      </c>
+      <c r="C320" t="s">
         <v>978</v>
       </c>
-      <c r="C320" t="s">
+      <c r="D320" t="s">
+        <v>50</v>
+      </c>
+      <c r="E320" t="s">
+        <v>12</v>
+      </c>
+      <c r="F320" t="s">
         <v>979</v>
       </c>
-      <c r="D320" t="s">
-        <v>11</v>
-      </c>
-      <c r="E320" t="s">
-        <v>12</v>
-      </c>
-      <c r="F320" t="s">
-        <v>980</v>
-      </c>
       <c r="G320" t="s">
         <v>14</v>
       </c>
       <c r="H320">
-        <v>104</v>
+        <v>183</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
+        <v>980</v>
+      </c>
+      <c r="B321" t="s">
+        <v>863</v>
+      </c>
+      <c r="C321" t="s">
         <v>981</v>
       </c>
-      <c r="B321" t="s">
-        <v>978</v>
-      </c>
-      <c r="C321" t="s">
+      <c r="D321" t="s">
+        <v>50</v>
+      </c>
+      <c r="E321" t="s">
+        <v>12</v>
+      </c>
+      <c r="F321" t="s">
         <v>982</v>
       </c>
-      <c r="D321" t="s">
-        <v>11</v>
-      </c>
-      <c r="E321" t="s">
-        <v>12</v>
-      </c>
-      <c r="F321" t="s">
-        <v>983</v>
-      </c>
       <c r="G321" t="s">
         <v>14</v>
       </c>
       <c r="H321">
-        <v>142</v>
+        <v>255</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>983</v>
+      </c>
+      <c r="B322" t="s">
         <v>984</v>
-      </c>
-      <c r="B322" t="s">
-        <v>978</v>
       </c>
       <c r="C322" t="s">
         <v>985</v>
@@ -13432,7 +13468,7 @@
         <v>14</v>
       </c>
       <c r="H322">
-        <v>167</v>
+        <v>231</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
@@ -13440,7 +13476,7 @@
         <v>987</v>
       </c>
       <c r="B323" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C323" t="s">
         <v>988</v>
@@ -13458,7 +13494,7 @@
         <v>14</v>
       </c>
       <c r="H323">
-        <v>107</v>
+        <v>265</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
@@ -13466,7 +13502,7 @@
         <v>990</v>
       </c>
       <c r="B324" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C324" t="s">
         <v>991</v>
@@ -13484,7 +13520,7 @@
         <v>14</v>
       </c>
       <c r="H324">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
@@ -13492,7 +13528,7 @@
         <v>993</v>
       </c>
       <c r="B325" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C325" t="s">
         <v>994</v>
@@ -13510,7 +13546,7 @@
         <v>14</v>
       </c>
       <c r="H325">
-        <v>92</v>
+        <v>162</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
@@ -13518,13 +13554,13 @@
         <v>996</v>
       </c>
       <c r="B326" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C326" t="s">
         <v>997</v>
       </c>
       <c r="D326" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E326" t="s">
         <v>12</v>
@@ -13536,7 +13572,7 @@
         <v>14</v>
       </c>
       <c r="H326">
-        <v>179</v>
+        <v>204</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
@@ -13544,13 +13580,13 @@
         <v>999</v>
       </c>
       <c r="B327" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C327" t="s">
         <v>1000</v>
       </c>
       <c r="D327" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E327" t="s">
         <v>12</v>
@@ -13562,7 +13598,7 @@
         <v>14</v>
       </c>
       <c r="H327">
-        <v>232</v>
+        <v>156</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
@@ -13570,7 +13606,7 @@
         <v>1002</v>
       </c>
       <c r="B328" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C328" t="s">
         <v>1003</v>
@@ -13588,7 +13624,7 @@
         <v>14</v>
       </c>
       <c r="H328">
-        <v>225</v>
+        <v>131</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
@@ -13596,7 +13632,7 @@
         <v>1005</v>
       </c>
       <c r="B329" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C329" t="s">
         <v>1006</v>
@@ -13614,7 +13650,7 @@
         <v>14</v>
       </c>
       <c r="H329">
-        <v>215</v>
+        <v>234</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
@@ -13622,7 +13658,7 @@
         <v>1008</v>
       </c>
       <c r="B330" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C330" t="s">
         <v>1009</v>
@@ -13640,7 +13676,7 @@
         <v>14</v>
       </c>
       <c r="H330">
-        <v>120</v>
+        <v>252</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
@@ -13648,7 +13684,7 @@
         <v>1011</v>
       </c>
       <c r="B331" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C331" t="s">
         <v>1012</v>
@@ -13666,7 +13702,7 @@
         <v>14</v>
       </c>
       <c r="H331">
-        <v>264</v>
+        <v>241</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
@@ -13674,7 +13710,7 @@
         <v>1014</v>
       </c>
       <c r="B332" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C332" t="s">
         <v>1015</v>
@@ -13692,7 +13728,7 @@
         <v>14</v>
       </c>
       <c r="H332">
-        <v>230</v>
+        <v>177</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
@@ -13700,7 +13736,7 @@
         <v>1017</v>
       </c>
       <c r="B333" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C333" t="s">
         <v>1018</v>
@@ -13718,7 +13754,7 @@
         <v>14</v>
       </c>
       <c r="H333">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
@@ -13726,7 +13762,7 @@
         <v>1020</v>
       </c>
       <c r="B334" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C334" t="s">
         <v>1021</v>
@@ -13744,7 +13780,7 @@
         <v>14</v>
       </c>
       <c r="H334">
-        <v>190</v>
+        <v>246</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
@@ -13752,7 +13788,7 @@
         <v>1023</v>
       </c>
       <c r="B335" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C335" t="s">
         <v>1024</v>
@@ -13770,7 +13806,7 @@
         <v>14</v>
       </c>
       <c r="H335">
-        <v>171</v>
+        <v>102</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
@@ -13778,7 +13814,7 @@
         <v>1026</v>
       </c>
       <c r="B336" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C336" t="s">
         <v>1027</v>
@@ -13796,7 +13832,7 @@
         <v>14</v>
       </c>
       <c r="H336">
-        <v>235</v>
+        <v>215</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
@@ -13804,7 +13840,7 @@
         <v>1029</v>
       </c>
       <c r="B337" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C337" t="s">
         <v>1030</v>
@@ -13822,7 +13858,7 @@
         <v>14</v>
       </c>
       <c r="H337">
-        <v>159</v>
+        <v>254</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
@@ -13830,7 +13866,7 @@
         <v>1032</v>
       </c>
       <c r="B338" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C338" t="s">
         <v>1033</v>
@@ -13848,7 +13884,7 @@
         <v>14</v>
       </c>
       <c r="H338">
-        <v>196</v>
+        <v>148</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
@@ -13856,45 +13892,45 @@
         <v>1035</v>
       </c>
       <c r="B339" t="s">
+        <v>984</v>
+      </c>
+      <c r="C339" t="s">
         <v>1036</v>
       </c>
-      <c r="C339" t="s">
+      <c r="D339" t="s">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>12</v>
+      </c>
+      <c r="F339" t="s">
         <v>1037</v>
       </c>
-      <c r="D339" t="s">
-        <v>11</v>
-      </c>
-      <c r="E339" t="s">
-        <v>12</v>
-      </c>
-      <c r="F339" t="s">
-        <v>1038</v>
-      </c>
       <c r="G339" t="s">
         <v>14</v>
       </c>
       <c r="H339">
-        <v>180</v>
+        <v>164</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B340" t="s">
+        <v>984</v>
+      </c>
+      <c r="C340" t="s">
         <v>1039</v>
       </c>
-      <c r="B340" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C340" t="s">
+      <c r="D340" t="s">
+        <v>50</v>
+      </c>
+      <c r="E340" t="s">
+        <v>12</v>
+      </c>
+      <c r="F340" t="s">
         <v>1040</v>
-      </c>
-      <c r="D340" t="s">
-        <v>11</v>
-      </c>
-      <c r="E340" t="s">
-        <v>12</v>
-      </c>
-      <c r="F340" t="s">
-        <v>1041</v>
       </c>
       <c r="G340" t="s">
         <v>14</v>
@@ -13905,36 +13941,36 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B341" t="s">
+        <v>984</v>
+      </c>
+      <c r="C341" t="s">
         <v>1042</v>
       </c>
-      <c r="B341" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C341" t="s">
+      <c r="D341" t="s">
+        <v>50</v>
+      </c>
+      <c r="E341" t="s">
+        <v>12</v>
+      </c>
+      <c r="F341" t="s">
         <v>1043</v>
       </c>
-      <c r="D341" t="s">
-        <v>11</v>
-      </c>
-      <c r="E341" t="s">
-        <v>12</v>
-      </c>
-      <c r="F341" t="s">
-        <v>1044</v>
-      </c>
       <c r="G341" t="s">
         <v>14</v>
       </c>
       <c r="H341">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B342" t="s">
         <v>1045</v>
-      </c>
-      <c r="B342" t="s">
-        <v>1036</v>
       </c>
       <c r="C342" t="s">
         <v>1046</v>
@@ -13952,7 +13988,7 @@
         <v>14</v>
       </c>
       <c r="H342">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
@@ -13960,7 +13996,7 @@
         <v>1048</v>
       </c>
       <c r="B343" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C343" t="s">
         <v>1049</v>
@@ -13978,7 +14014,7 @@
         <v>14</v>
       </c>
       <c r="H343">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
@@ -13986,7 +14022,7 @@
         <v>1051</v>
       </c>
       <c r="B344" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C344" t="s">
         <v>1052</v>
@@ -14004,7 +14040,7 @@
         <v>14</v>
       </c>
       <c r="H344">
-        <v>238</v>
+        <v>211</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
@@ -14012,13 +14048,13 @@
         <v>1054</v>
       </c>
       <c r="B345" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C345" t="s">
         <v>1055</v>
       </c>
       <c r="D345" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E345" t="s">
         <v>12</v>
@@ -14030,7 +14066,7 @@
         <v>14</v>
       </c>
       <c r="H345">
-        <v>156</v>
+        <v>210</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
@@ -14038,13 +14074,13 @@
         <v>1057</v>
       </c>
       <c r="B346" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C346" t="s">
         <v>1058</v>
       </c>
       <c r="D346" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E346" t="s">
         <v>12</v>
@@ -14056,7 +14092,7 @@
         <v>14</v>
       </c>
       <c r="H346">
-        <v>208</v>
+        <v>115</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
@@ -14064,13 +14100,13 @@
         <v>1060</v>
       </c>
       <c r="B347" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C347" t="s">
         <v>1061</v>
       </c>
       <c r="D347" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E347" t="s">
         <v>12</v>
@@ -14082,7 +14118,7 @@
         <v>14</v>
       </c>
       <c r="H347">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
@@ -14090,7 +14126,7 @@
         <v>1063</v>
       </c>
       <c r="B348" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C348" t="s">
         <v>1064</v>
@@ -14108,7 +14144,7 @@
         <v>14</v>
       </c>
       <c r="H348">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
@@ -14116,7 +14152,7 @@
         <v>1066</v>
       </c>
       <c r="B349" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C349" t="s">
         <v>1067</v>
@@ -14134,7 +14170,7 @@
         <v>14</v>
       </c>
       <c r="H349">
-        <v>228</v>
+        <v>158</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
@@ -14142,7 +14178,7 @@
         <v>1069</v>
       </c>
       <c r="B350" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C350" t="s">
         <v>1070</v>
@@ -14160,7 +14196,7 @@
         <v>14</v>
       </c>
       <c r="H350">
-        <v>199</v>
+        <v>153</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
@@ -14168,7 +14204,7 @@
         <v>1072</v>
       </c>
       <c r="B351" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C351" t="s">
         <v>1073</v>
@@ -14186,7 +14222,7 @@
         <v>14</v>
       </c>
       <c r="H351">
-        <v>147</v>
+        <v>162</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
@@ -14194,7 +14230,7 @@
         <v>1075</v>
       </c>
       <c r="B352" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C352" t="s">
         <v>1076</v>
@@ -14212,7 +14248,7 @@
         <v>14</v>
       </c>
       <c r="H352">
-        <v>196</v>
+        <v>111</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
@@ -14220,7 +14256,7 @@
         <v>1078</v>
       </c>
       <c r="B353" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C353" t="s">
         <v>1079</v>
@@ -14238,7 +14274,7 @@
         <v>14</v>
       </c>
       <c r="H353">
-        <v>217</v>
+        <v>131</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
@@ -14246,7 +14282,7 @@
         <v>1081</v>
       </c>
       <c r="B354" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C354" t="s">
         <v>1082</v>
@@ -14264,7 +14300,7 @@
         <v>14</v>
       </c>
       <c r="H354">
-        <v>233</v>
+        <v>197</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
@@ -14272,7 +14308,7 @@
         <v>1084</v>
       </c>
       <c r="B355" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C355" t="s">
         <v>1085</v>
@@ -14290,7 +14326,7 @@
         <v>14</v>
       </c>
       <c r="H355">
-        <v>191</v>
+        <v>159</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
@@ -14298,7 +14334,7 @@
         <v>1087</v>
       </c>
       <c r="B356" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C356" t="s">
         <v>1088</v>
@@ -14316,7 +14352,7 @@
         <v>14</v>
       </c>
       <c r="H356">
-        <v>128</v>
+        <v>212</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
@@ -14324,7 +14360,7 @@
         <v>1090</v>
       </c>
       <c r="B357" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C357" t="s">
         <v>1091</v>
@@ -14342,7 +14378,7 @@
         <v>14</v>
       </c>
       <c r="H357">
-        <v>245</v>
+        <v>158</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
@@ -14350,7 +14386,7 @@
         <v>1093</v>
       </c>
       <c r="B358" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="C358" t="s">
         <v>1094</v>
@@ -14368,7 +14404,7 @@
         <v>14</v>
       </c>
       <c r="H358">
-        <v>186</v>
+        <v>200</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
@@ -14376,85 +14412,85 @@
         <v>1096</v>
       </c>
       <c r="B359" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C359" t="s">
         <v>1097</v>
       </c>
-      <c r="C359" t="s">
+      <c r="D359" t="s">
+        <v>50</v>
+      </c>
+      <c r="E359" t="s">
+        <v>12</v>
+      </c>
+      <c r="F359" t="s">
         <v>1098</v>
       </c>
-      <c r="D359" t="s">
-        <v>11</v>
-      </c>
-      <c r="E359" t="s">
-        <v>12</v>
-      </c>
-      <c r="F359" t="s">
-        <v>1099</v>
-      </c>
       <c r="G359" t="s">
         <v>14</v>
       </c>
       <c r="H359">
-        <v>227</v>
+        <v>134</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C360" t="s">
         <v>1100</v>
       </c>
-      <c r="B360" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C360" t="s">
+      <c r="D360" t="s">
+        <v>50</v>
+      </c>
+      <c r="E360" t="s">
+        <v>12</v>
+      </c>
+      <c r="F360" t="s">
         <v>1101</v>
       </c>
-      <c r="D360" t="s">
-        <v>11</v>
-      </c>
-      <c r="E360" t="s">
-        <v>12</v>
-      </c>
-      <c r="F360" t="s">
-        <v>1102</v>
-      </c>
       <c r="G360" t="s">
         <v>14</v>
       </c>
       <c r="H360">
-        <v>212</v>
+        <v>152</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C361" t="s">
         <v>1103</v>
       </c>
-      <c r="B361" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C361" t="s">
+      <c r="D361" t="s">
+        <v>50</v>
+      </c>
+      <c r="E361" t="s">
+        <v>12</v>
+      </c>
+      <c r="F361" t="s">
         <v>1104</v>
       </c>
-      <c r="D361" t="s">
-        <v>11</v>
-      </c>
-      <c r="E361" t="s">
-        <v>12</v>
-      </c>
-      <c r="F361" t="s">
-        <v>1105</v>
-      </c>
       <c r="G361" t="s">
         <v>14</v>
       </c>
       <c r="H361">
-        <v>256</v>
+        <v>231</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B362" t="s">
         <v>1106</v>
-      </c>
-      <c r="B362" t="s">
-        <v>1097</v>
       </c>
       <c r="C362" t="s">
         <v>1107</v>
@@ -14472,7 +14508,7 @@
         <v>14</v>
       </c>
       <c r="H362">
-        <v>131</v>
+        <v>254</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
@@ -14480,7 +14516,7 @@
         <v>1109</v>
       </c>
       <c r="B363" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C363" t="s">
         <v>1110</v>
@@ -14498,7 +14534,7 @@
         <v>14</v>
       </c>
       <c r="H363">
-        <v>105</v>
+        <v>169</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
@@ -14506,7 +14542,7 @@
         <v>1112</v>
       </c>
       <c r="B364" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C364" t="s">
         <v>1113</v>
@@ -14524,7 +14560,7 @@
         <v>14</v>
       </c>
       <c r="H364">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
@@ -14532,13 +14568,13 @@
         <v>1115</v>
       </c>
       <c r="B365" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C365" t="s">
         <v>1116</v>
       </c>
       <c r="D365" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E365" t="s">
         <v>12</v>
@@ -14550,7 +14586,7 @@
         <v>14</v>
       </c>
       <c r="H365">
-        <v>255</v>
+        <v>225</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
@@ -14558,13 +14594,13 @@
         <v>1118</v>
       </c>
       <c r="B366" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C366" t="s">
         <v>1119</v>
       </c>
       <c r="D366" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E366" t="s">
         <v>12</v>
@@ -14576,7 +14612,7 @@
         <v>14</v>
       </c>
       <c r="H366">
-        <v>237</v>
+        <v>148</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
@@ -14584,13 +14620,13 @@
         <v>1121</v>
       </c>
       <c r="B367" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C367" t="s">
         <v>1122</v>
       </c>
       <c r="D367" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E367" t="s">
         <v>12</v>
@@ -14602,7 +14638,7 @@
         <v>14</v>
       </c>
       <c r="H367">
-        <v>226</v>
+        <v>134</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
@@ -14610,7 +14646,7 @@
         <v>1124</v>
       </c>
       <c r="B368" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C368" t="s">
         <v>1125</v>
@@ -14628,7 +14664,7 @@
         <v>14</v>
       </c>
       <c r="H368">
-        <v>210</v>
+        <v>147</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
@@ -14636,7 +14672,7 @@
         <v>1127</v>
       </c>
       <c r="B369" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C369" t="s">
         <v>1128</v>
@@ -14654,7 +14690,7 @@
         <v>14</v>
       </c>
       <c r="H369">
-        <v>228</v>
+        <v>211</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
@@ -14662,7 +14698,7 @@
         <v>1130</v>
       </c>
       <c r="B370" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C370" t="s">
         <v>1131</v>
@@ -14680,7 +14716,7 @@
         <v>14</v>
       </c>
       <c r="H370">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
@@ -14688,7 +14724,7 @@
         <v>1133</v>
       </c>
       <c r="B371" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C371" t="s">
         <v>1134</v>
@@ -14706,7 +14742,7 @@
         <v>14</v>
       </c>
       <c r="H371">
-        <v>101</v>
+        <v>147</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
@@ -14714,7 +14750,7 @@
         <v>1136</v>
       </c>
       <c r="B372" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C372" t="s">
         <v>1137</v>
@@ -14732,7 +14768,7 @@
         <v>14</v>
       </c>
       <c r="H372">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
@@ -14740,7 +14776,7 @@
         <v>1139</v>
       </c>
       <c r="B373" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C373" t="s">
         <v>1140</v>
@@ -14758,7 +14794,7 @@
         <v>14</v>
       </c>
       <c r="H373">
-        <v>204</v>
+        <v>266</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
@@ -14766,7 +14802,7 @@
         <v>1142</v>
       </c>
       <c r="B374" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C374" t="s">
         <v>1143</v>
@@ -14784,7 +14820,7 @@
         <v>14</v>
       </c>
       <c r="H374">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
@@ -14792,7 +14828,7 @@
         <v>1145</v>
       </c>
       <c r="B375" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C375" t="s">
         <v>1146</v>
@@ -14810,7 +14846,7 @@
         <v>14</v>
       </c>
       <c r="H375">
-        <v>266</v>
+        <v>141</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
@@ -14818,7 +14854,7 @@
         <v>1148</v>
       </c>
       <c r="B376" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C376" t="s">
         <v>1149</v>
@@ -14836,7 +14872,7 @@
         <v>14</v>
       </c>
       <c r="H376">
-        <v>251</v>
+        <v>146</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
@@ -14844,7 +14880,7 @@
         <v>1151</v>
       </c>
       <c r="B377" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C377" t="s">
         <v>1152</v>
@@ -14862,7 +14898,7 @@
         <v>14</v>
       </c>
       <c r="H377">
-        <v>215</v>
+        <v>132</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
@@ -14870,7 +14906,7 @@
         <v>1154</v>
       </c>
       <c r="B378" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="C378" t="s">
         <v>1155</v>
@@ -14888,7 +14924,7 @@
         <v>14</v>
       </c>
       <c r="H378">
-        <v>200</v>
+        <v>126</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
@@ -14896,85 +14932,85 @@
         <v>1157</v>
       </c>
       <c r="B379" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C379" t="s">
         <v>1158</v>
       </c>
-      <c r="C379" t="s">
+      <c r="D379" t="s">
+        <v>50</v>
+      </c>
+      <c r="E379" t="s">
+        <v>12</v>
+      </c>
+      <c r="F379" t="s">
         <v>1159</v>
       </c>
-      <c r="D379" t="s">
-        <v>11</v>
-      </c>
-      <c r="E379" t="s">
-        <v>12</v>
-      </c>
-      <c r="F379" t="s">
-        <v>1160</v>
-      </c>
       <c r="G379" t="s">
         <v>14</v>
       </c>
       <c r="H379">
-        <v>98</v>
+        <v>195</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B380" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C380" t="s">
         <v>1161</v>
       </c>
-      <c r="B380" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C380" t="s">
+      <c r="D380" t="s">
+        <v>50</v>
+      </c>
+      <c r="E380" t="s">
+        <v>12</v>
+      </c>
+      <c r="F380" t="s">
         <v>1162</v>
       </c>
-      <c r="D380" t="s">
-        <v>11</v>
-      </c>
-      <c r="E380" t="s">
-        <v>12</v>
-      </c>
-      <c r="F380" t="s">
-        <v>1163</v>
-      </c>
       <c r="G380" t="s">
         <v>14</v>
       </c>
       <c r="H380">
-        <v>261</v>
+        <v>228</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B381" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C381" t="s">
         <v>1164</v>
       </c>
-      <c r="B381" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C381" t="s">
+      <c r="D381" t="s">
+        <v>50</v>
+      </c>
+      <c r="E381" t="s">
+        <v>12</v>
+      </c>
+      <c r="F381" t="s">
         <v>1165</v>
       </c>
-      <c r="D381" t="s">
-        <v>11</v>
-      </c>
-      <c r="E381" t="s">
-        <v>12</v>
-      </c>
-      <c r="F381" t="s">
-        <v>1166</v>
-      </c>
       <c r="G381" t="s">
         <v>14</v>
       </c>
       <c r="H381">
-        <v>243</v>
+        <v>124</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B382" t="s">
         <v>1167</v>
-      </c>
-      <c r="B382" t="s">
-        <v>1158</v>
       </c>
       <c r="C382" t="s">
         <v>1168</v>
@@ -14992,7 +15028,7 @@
         <v>14</v>
       </c>
       <c r="H382">
-        <v>247</v>
+        <v>218</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
@@ -15000,7 +15036,7 @@
         <v>1170</v>
       </c>
       <c r="B383" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C383" t="s">
         <v>1171</v>
@@ -15018,7 +15054,7 @@
         <v>14</v>
       </c>
       <c r="H383">
-        <v>198</v>
+        <v>96</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
@@ -15026,13 +15062,13 @@
         <v>1173</v>
       </c>
       <c r="B384" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C384" t="s">
         <v>1174</v>
       </c>
       <c r="D384" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E384" t="s">
         <v>12</v>
@@ -15044,7 +15080,7 @@
         <v>14</v>
       </c>
       <c r="H384">
-        <v>163</v>
+        <v>208</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
@@ -15052,13 +15088,13 @@
         <v>1176</v>
       </c>
       <c r="B385" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C385" t="s">
         <v>1177</v>
       </c>
       <c r="D385" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E385" t="s">
         <v>12</v>
@@ -15070,7 +15106,7 @@
         <v>14</v>
       </c>
       <c r="H385">
-        <v>96</v>
+        <v>187</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
@@ -15078,13 +15114,13 @@
         <v>1179</v>
       </c>
       <c r="B386" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C386" t="s">
         <v>1180</v>
       </c>
       <c r="D386" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E386" t="s">
         <v>12</v>
@@ -15096,7 +15132,7 @@
         <v>14</v>
       </c>
       <c r="H386">
-        <v>132</v>
+        <v>245</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
@@ -15104,13 +15140,13 @@
         <v>1182</v>
       </c>
       <c r="B387" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C387" t="s">
         <v>1183</v>
       </c>
       <c r="D387" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E387" t="s">
         <v>12</v>
@@ -15122,7 +15158,7 @@
         <v>14</v>
       </c>
       <c r="H387">
-        <v>227</v>
+        <v>173</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
@@ -15130,7 +15166,7 @@
         <v>1185</v>
       </c>
       <c r="B388" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C388" t="s">
         <v>1186</v>
@@ -15148,7 +15184,7 @@
         <v>14</v>
       </c>
       <c r="H388">
-        <v>203</v>
+        <v>237</v>
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
@@ -15156,7 +15192,7 @@
         <v>1188</v>
       </c>
       <c r="B389" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C389" t="s">
         <v>1189</v>
@@ -15174,7 +15210,7 @@
         <v>14</v>
       </c>
       <c r="H389">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
@@ -15182,7 +15218,7 @@
         <v>1191</v>
       </c>
       <c r="B390" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C390" t="s">
         <v>1192</v>
@@ -15200,7 +15236,7 @@
         <v>14</v>
       </c>
       <c r="H390">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
@@ -15208,7 +15244,7 @@
         <v>1194</v>
       </c>
       <c r="B391" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C391" t="s">
         <v>1195</v>
@@ -15226,7 +15262,7 @@
         <v>14</v>
       </c>
       <c r="H391">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
@@ -15234,7 +15270,7 @@
         <v>1197</v>
       </c>
       <c r="B392" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C392" t="s">
         <v>1198</v>
@@ -15252,7 +15288,7 @@
         <v>14</v>
       </c>
       <c r="H392">
-        <v>128</v>
+        <v>242</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
@@ -15260,7 +15296,7 @@
         <v>1200</v>
       </c>
       <c r="B393" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C393" t="s">
         <v>1201</v>
@@ -15278,7 +15314,7 @@
         <v>14</v>
       </c>
       <c r="H393">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
@@ -15286,7 +15322,7 @@
         <v>1203</v>
       </c>
       <c r="B394" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C394" t="s">
         <v>1204</v>
@@ -15304,7 +15340,7 @@
         <v>14</v>
       </c>
       <c r="H394">
-        <v>124</v>
+        <v>257</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
@@ -15312,7 +15348,7 @@
         <v>1206</v>
       </c>
       <c r="B395" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C395" t="s">
         <v>1207</v>
@@ -15330,7 +15366,7 @@
         <v>14</v>
       </c>
       <c r="H395">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
@@ -15338,7 +15374,7 @@
         <v>1209</v>
       </c>
       <c r="B396" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C396" t="s">
         <v>1210</v>
@@ -15356,7 +15392,7 @@
         <v>14</v>
       </c>
       <c r="H396">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
@@ -15364,7 +15400,7 @@
         <v>1212</v>
       </c>
       <c r="B397" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="C397" t="s">
         <v>1213</v>
@@ -15382,7 +15418,7 @@
         <v>14</v>
       </c>
       <c r="H397">
-        <v>103</v>
+        <v>228</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
@@ -15390,117 +15426,117 @@
         <v>1215</v>
       </c>
       <c r="B398" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C398" t="s">
         <v>1216</v>
       </c>
-      <c r="C398" t="s">
+      <c r="D398" t="s">
+        <v>50</v>
+      </c>
+      <c r="E398" t="s">
+        <v>12</v>
+      </c>
+      <c r="F398" t="s">
         <v>1217</v>
       </c>
-      <c r="D398" t="s">
-        <v>11</v>
-      </c>
-      <c r="E398" t="s">
-        <v>12</v>
-      </c>
-      <c r="F398" t="s">
-        <v>1218</v>
-      </c>
       <c r="G398" t="s">
         <v>14</v>
       </c>
       <c r="H398">
-        <v>122</v>
+        <v>257</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C399" t="s">
         <v>1219</v>
       </c>
-      <c r="B399" t="s">
-        <v>1216</v>
-      </c>
-      <c r="C399" t="s">
+      <c r="D399" t="s">
+        <v>50</v>
+      </c>
+      <c r="E399" t="s">
+        <v>12</v>
+      </c>
+      <c r="F399" t="s">
         <v>1220</v>
       </c>
-      <c r="D399" t="s">
-        <v>11</v>
-      </c>
-      <c r="E399" t="s">
-        <v>12</v>
-      </c>
-      <c r="F399" t="s">
-        <v>1221</v>
-      </c>
       <c r="G399" t="s">
         <v>14</v>
       </c>
       <c r="H399">
-        <v>93</v>
+        <v>178</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C400" t="s">
         <v>1222</v>
       </c>
-      <c r="B400" t="s">
-        <v>1216</v>
-      </c>
-      <c r="C400" t="s">
+      <c r="D400" t="s">
+        <v>50</v>
+      </c>
+      <c r="E400" t="s">
+        <v>12</v>
+      </c>
+      <c r="F400" t="s">
         <v>1223</v>
       </c>
-      <c r="D400" t="s">
-        <v>11</v>
-      </c>
-      <c r="E400" t="s">
-        <v>12</v>
-      </c>
-      <c r="F400" t="s">
-        <v>1224</v>
-      </c>
       <c r="G400" t="s">
         <v>14</v>
       </c>
       <c r="H400">
-        <v>265</v>
+        <v>166</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B401" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C401" t="s">
         <v>1225</v>
       </c>
-      <c r="B401" t="s">
-        <v>1216</v>
-      </c>
-      <c r="C401" t="s">
+      <c r="D401" t="s">
+        <v>50</v>
+      </c>
+      <c r="E401" t="s">
+        <v>12</v>
+      </c>
+      <c r="F401" t="s">
         <v>1226</v>
       </c>
-      <c r="D401" t="s">
-        <v>50</v>
-      </c>
-      <c r="E401" t="s">
-        <v>12</v>
-      </c>
-      <c r="F401" t="s">
-        <v>1227</v>
-      </c>
       <c r="G401" t="s">
         <v>14</v>
       </c>
       <c r="H401">
-        <v>203</v>
+        <v>120</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B402" t="s">
         <v>1228</v>
-      </c>
-      <c r="B402" t="s">
-        <v>1216</v>
       </c>
       <c r="C402" t="s">
         <v>1229</v>
       </c>
       <c r="D402" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E402" t="s">
         <v>12</v>
@@ -15512,7 +15548,7 @@
         <v>14</v>
       </c>
       <c r="H402">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
@@ -15520,13 +15556,13 @@
         <v>1231</v>
       </c>
       <c r="B403" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="C403" t="s">
         <v>1232</v>
       </c>
       <c r="D403" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E403" t="s">
         <v>12</v>
@@ -15538,7 +15574,7 @@
         <v>14</v>
       </c>
       <c r="H403">
-        <v>91</v>
+        <v>231</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.25">
@@ -15546,13 +15582,13 @@
         <v>1234</v>
       </c>
       <c r="B404" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="C404" t="s">
         <v>1235</v>
       </c>
       <c r="D404" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E404" t="s">
         <v>12</v>
@@ -15564,7 +15600,7 @@
         <v>14</v>
       </c>
       <c r="H404">
-        <v>114</v>
+        <v>203</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
@@ -15572,7 +15608,7 @@
         <v>1237</v>
       </c>
       <c r="B405" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="C405" t="s">
         <v>1238</v>
@@ -15590,7 +15626,7 @@
         <v>14</v>
       </c>
       <c r="H405">
-        <v>212</v>
+        <v>110</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.25">
@@ -15598,7 +15634,7 @@
         <v>1240</v>
       </c>
       <c r="B406" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="C406" t="s">
         <v>1241</v>
@@ -15616,7 +15652,7 @@
         <v>14</v>
       </c>
       <c r="H406">
-        <v>104</v>
+        <v>127</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
@@ -15624,7 +15660,7 @@
         <v>1243</v>
       </c>
       <c r="B407" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="C407" t="s">
         <v>1244</v>
@@ -15642,7 +15678,7 @@
         <v>14</v>
       </c>
       <c r="H407">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
@@ -15650,111 +15686,111 @@
         <v>1246</v>
       </c>
       <c r="B408" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C408" t="s">
         <v>1247</v>
       </c>
-      <c r="C408" t="s">
+      <c r="D408" t="s">
+        <v>50</v>
+      </c>
+      <c r="E408" t="s">
+        <v>12</v>
+      </c>
+      <c r="F408" t="s">
         <v>1248</v>
       </c>
-      <c r="D408" t="s">
-        <v>11</v>
-      </c>
-      <c r="E408" t="s">
-        <v>12</v>
-      </c>
-      <c r="F408" t="s">
-        <v>1249</v>
-      </c>
       <c r="G408" t="s">
         <v>14</v>
       </c>
       <c r="H408">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C409" t="s">
         <v>1250</v>
       </c>
-      <c r="B409" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C409" t="s">
+      <c r="D409" t="s">
+        <v>50</v>
+      </c>
+      <c r="E409" t="s">
+        <v>12</v>
+      </c>
+      <c r="F409" t="s">
         <v>1251</v>
       </c>
-      <c r="D409" t="s">
-        <v>11</v>
-      </c>
-      <c r="E409" t="s">
-        <v>12</v>
-      </c>
-      <c r="F409" t="s">
-        <v>1252</v>
-      </c>
       <c r="G409" t="s">
         <v>14</v>
       </c>
       <c r="H409">
-        <v>111</v>
+        <v>249</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C410" t="s">
         <v>1253</v>
       </c>
-      <c r="B410" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C410" t="s">
+      <c r="D410" t="s">
+        <v>50</v>
+      </c>
+      <c r="E410" t="s">
+        <v>12</v>
+      </c>
+      <c r="F410" t="s">
         <v>1254</v>
       </c>
-      <c r="D410" t="s">
-        <v>11</v>
-      </c>
-      <c r="E410" t="s">
-        <v>12</v>
-      </c>
-      <c r="F410" t="s">
-        <v>1255</v>
-      </c>
       <c r="G410" t="s">
         <v>14</v>
       </c>
       <c r="H410">
-        <v>196</v>
+        <v>113</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C411" t="s">
         <v>1256</v>
       </c>
-      <c r="B411" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C411" t="s">
+      <c r="D411" t="s">
+        <v>50</v>
+      </c>
+      <c r="E411" t="s">
+        <v>12</v>
+      </c>
+      <c r="F411" t="s">
         <v>1257</v>
       </c>
-      <c r="D411" t="s">
-        <v>11</v>
-      </c>
-      <c r="E411" t="s">
-        <v>12</v>
-      </c>
-      <c r="F411" t="s">
-        <v>1258</v>
-      </c>
       <c r="G411" t="s">
         <v>14</v>
       </c>
       <c r="H411">
-        <v>207</v>
+        <v>146</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B412" t="s">
         <v>1259</v>
-      </c>
-      <c r="B412" t="s">
-        <v>1247</v>
       </c>
       <c r="C412" t="s">
         <v>1260</v>
@@ -15772,7 +15808,7 @@
         <v>14</v>
       </c>
       <c r="H412">
-        <v>210</v>
+        <v>251</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
@@ -15780,7 +15816,7 @@
         <v>1262</v>
       </c>
       <c r="B413" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C413" t="s">
         <v>1263</v>
@@ -15798,7 +15834,7 @@
         <v>14</v>
       </c>
       <c r="H413">
-        <v>161</v>
+        <v>124</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
@@ -15806,13 +15842,13 @@
         <v>1265</v>
       </c>
       <c r="B414" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C414" t="s">
         <v>1266</v>
       </c>
       <c r="D414" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E414" t="s">
         <v>12</v>
@@ -15824,7 +15860,7 @@
         <v>14</v>
       </c>
       <c r="H414">
-        <v>216</v>
+        <v>193</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
@@ -15832,13 +15868,13 @@
         <v>1268</v>
       </c>
       <c r="B415" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C415" t="s">
         <v>1269</v>
       </c>
       <c r="D415" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E415" t="s">
         <v>12</v>
@@ -15850,7 +15886,7 @@
         <v>14</v>
       </c>
       <c r="H415">
-        <v>143</v>
+        <v>162</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.25">
@@ -15858,13 +15894,13 @@
         <v>1271</v>
       </c>
       <c r="B416" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C416" t="s">
         <v>1272</v>
       </c>
       <c r="D416" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E416" t="s">
         <v>12</v>
@@ -15876,7 +15912,7 @@
         <v>14</v>
       </c>
       <c r="H416">
-        <v>109</v>
+        <v>196</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
@@ -15884,13 +15920,13 @@
         <v>1274</v>
       </c>
       <c r="B417" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C417" t="s">
         <v>1275</v>
       </c>
       <c r="D417" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E417" t="s">
         <v>12</v>
@@ -15902,7 +15938,7 @@
         <v>14</v>
       </c>
       <c r="H417">
-        <v>208</v>
+        <v>188</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
@@ -15910,7 +15946,7 @@
         <v>1277</v>
       </c>
       <c r="B418" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C418" t="s">
         <v>1278</v>
@@ -15928,7 +15964,7 @@
         <v>14</v>
       </c>
       <c r="H418">
-        <v>120</v>
+        <v>252</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.25">
@@ -15936,7 +15972,7 @@
         <v>1280</v>
       </c>
       <c r="B419" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C419" t="s">
         <v>1281</v>
@@ -15954,7 +15990,7 @@
         <v>14</v>
       </c>
       <c r="H419">
-        <v>95</v>
+        <v>263</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
@@ -15962,7 +15998,7 @@
         <v>1283</v>
       </c>
       <c r="B420" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C420" t="s">
         <v>1284</v>
@@ -15980,7 +16016,7 @@
         <v>14</v>
       </c>
       <c r="H420">
-        <v>188</v>
+        <v>135</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
@@ -15988,7 +16024,7 @@
         <v>1286</v>
       </c>
       <c r="B421" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C421" t="s">
         <v>1287</v>
@@ -16006,7 +16042,7 @@
         <v>14</v>
       </c>
       <c r="H421">
-        <v>140</v>
+        <v>215</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.25">
@@ -16014,7 +16050,7 @@
         <v>1289</v>
       </c>
       <c r="B422" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C422" t="s">
         <v>1290</v>
@@ -16032,7 +16068,7 @@
         <v>14</v>
       </c>
       <c r="H422">
-        <v>242</v>
+        <v>150</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
@@ -16040,7 +16076,7 @@
         <v>1292</v>
       </c>
       <c r="B423" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C423" t="s">
         <v>1293</v>
@@ -16058,7 +16094,7 @@
         <v>14</v>
       </c>
       <c r="H423">
-        <v>266</v>
+        <v>116</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.25">
@@ -16066,7 +16102,7 @@
         <v>1295</v>
       </c>
       <c r="B424" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C424" t="s">
         <v>1296</v>
@@ -16084,7 +16120,7 @@
         <v>14</v>
       </c>
       <c r="H424">
-        <v>260</v>
+        <v>184</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
@@ -16092,7 +16128,7 @@
         <v>1298</v>
       </c>
       <c r="B425" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C425" t="s">
         <v>1299</v>
@@ -16110,7 +16146,7 @@
         <v>14</v>
       </c>
       <c r="H425">
-        <v>126</v>
+        <v>147</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
@@ -16118,7 +16154,7 @@
         <v>1301</v>
       </c>
       <c r="B426" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C426" t="s">
         <v>1302</v>
@@ -16136,7 +16172,7 @@
         <v>14</v>
       </c>
       <c r="H426">
-        <v>118</v>
+        <v>146</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
@@ -16144,7 +16180,7 @@
         <v>1304</v>
       </c>
       <c r="B427" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C427" t="s">
         <v>1305</v>
@@ -16162,7 +16198,7 @@
         <v>14</v>
       </c>
       <c r="H427">
-        <v>259</v>
+        <v>90</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.25">
@@ -16170,97 +16206,97 @@
         <v>1307</v>
       </c>
       <c r="B428" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C428" t="s">
         <v>1308</v>
       </c>
-      <c r="C428" t="s">
+      <c r="D428" t="s">
+        <v>50</v>
+      </c>
+      <c r="E428" t="s">
+        <v>12</v>
+      </c>
+      <c r="F428" t="s">
         <v>1309</v>
       </c>
-      <c r="D428" t="s">
-        <v>11</v>
-      </c>
-      <c r="E428" t="s">
-        <v>12</v>
-      </c>
-      <c r="F428" t="s">
-        <v>1310</v>
-      </c>
       <c r="G428" t="s">
         <v>14</v>
       </c>
       <c r="H428">
-        <v>153</v>
+        <v>105</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C429" t="s">
         <v>1311</v>
       </c>
-      <c r="B429" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C429" t="s">
+      <c r="D429" t="s">
+        <v>50</v>
+      </c>
+      <c r="E429" t="s">
+        <v>12</v>
+      </c>
+      <c r="F429" t="s">
         <v>1312</v>
       </c>
-      <c r="D429" t="s">
-        <v>11</v>
-      </c>
-      <c r="E429" t="s">
-        <v>12</v>
-      </c>
-      <c r="F429" t="s">
-        <v>1313</v>
-      </c>
       <c r="G429" t="s">
         <v>14</v>
       </c>
       <c r="H429">
-        <v>146</v>
+        <v>249</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C430" t="s">
         <v>1314</v>
       </c>
-      <c r="B430" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C430" t="s">
+      <c r="D430" t="s">
+        <v>50</v>
+      </c>
+      <c r="E430" t="s">
+        <v>12</v>
+      </c>
+      <c r="F430" t="s">
         <v>1315</v>
       </c>
-      <c r="D430" t="s">
-        <v>11</v>
-      </c>
-      <c r="E430" t="s">
-        <v>12</v>
-      </c>
-      <c r="F430" t="s">
-        <v>1316</v>
-      </c>
       <c r="G430" t="s">
         <v>14</v>
       </c>
       <c r="H430">
-        <v>242</v>
+        <v>180</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C431" t="s">
         <v>1317</v>
       </c>
-      <c r="B431" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C431" t="s">
+      <c r="D431" t="s">
+        <v>50</v>
+      </c>
+      <c r="E431" t="s">
+        <v>12</v>
+      </c>
+      <c r="F431" t="s">
         <v>1318</v>
-      </c>
-      <c r="D431" t="s">
-        <v>50</v>
-      </c>
-      <c r="E431" t="s">
-        <v>12</v>
-      </c>
-      <c r="F431" t="s">
-        <v>1319</v>
       </c>
       <c r="G431" t="s">
         <v>14</v>
@@ -16271,16 +16307,16 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B432" t="s">
         <v>1320</v>
-      </c>
-      <c r="B432" t="s">
-        <v>1308</v>
       </c>
       <c r="C432" t="s">
         <v>1321</v>
       </c>
       <c r="D432" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E432" t="s">
         <v>12</v>
@@ -16292,7 +16328,7 @@
         <v>14</v>
       </c>
       <c r="H432">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.25">
@@ -16300,13 +16336,13 @@
         <v>1323</v>
       </c>
       <c r="B433" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="C433" t="s">
         <v>1324</v>
       </c>
       <c r="D433" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E433" t="s">
         <v>12</v>
@@ -16318,7 +16354,7 @@
         <v>14</v>
       </c>
       <c r="H433">
-        <v>93</v>
+        <v>210</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.25">
@@ -16326,13 +16362,13 @@
         <v>1326</v>
       </c>
       <c r="B434" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="C434" t="s">
         <v>1327</v>
       </c>
       <c r="D434" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E434" t="s">
         <v>12</v>
@@ -16344,7 +16380,7 @@
         <v>14</v>
       </c>
       <c r="H434">
-        <v>215</v>
+        <v>264</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
@@ -16352,7 +16388,7 @@
         <v>1329</v>
       </c>
       <c r="B435" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="C435" t="s">
         <v>1330</v>
@@ -16370,7 +16406,7 @@
         <v>14</v>
       </c>
       <c r="H435">
-        <v>266</v>
+        <v>222</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
@@ -16378,7 +16414,7 @@
         <v>1332</v>
       </c>
       <c r="B436" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="C436" t="s">
         <v>1333</v>
@@ -16396,7 +16432,7 @@
         <v>14</v>
       </c>
       <c r="H436">
-        <v>185</v>
+        <v>117</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.25">
@@ -16404,7 +16440,7 @@
         <v>1335</v>
       </c>
       <c r="B437" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="C437" t="s">
         <v>1336</v>
@@ -16422,7 +16458,7 @@
         <v>14</v>
       </c>
       <c r="H437">
-        <v>262</v>
+        <v>152</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.25">
@@ -16430,111 +16466,111 @@
         <v>1338</v>
       </c>
       <c r="B438" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C438" t="s">
         <v>1339</v>
       </c>
-      <c r="C438" t="s">
+      <c r="D438" t="s">
+        <v>50</v>
+      </c>
+      <c r="E438" t="s">
+        <v>12</v>
+      </c>
+      <c r="F438" t="s">
         <v>1340</v>
       </c>
-      <c r="D438" t="s">
-        <v>11</v>
-      </c>
-      <c r="E438" t="s">
-        <v>12</v>
-      </c>
-      <c r="F438" t="s">
-        <v>1341</v>
-      </c>
       <c r="G438" t="s">
         <v>14</v>
       </c>
       <c r="H438">
-        <v>187</v>
+        <v>241</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C439" t="s">
         <v>1342</v>
       </c>
-      <c r="B439" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C439" t="s">
+      <c r="D439" t="s">
+        <v>50</v>
+      </c>
+      <c r="E439" t="s">
+        <v>12</v>
+      </c>
+      <c r="F439" t="s">
         <v>1343</v>
       </c>
-      <c r="D439" t="s">
-        <v>11</v>
-      </c>
-      <c r="E439" t="s">
-        <v>12</v>
-      </c>
-      <c r="F439" t="s">
-        <v>1344</v>
-      </c>
       <c r="G439" t="s">
         <v>14</v>
       </c>
       <c r="H439">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C440" t="s">
         <v>1345</v>
       </c>
-      <c r="B440" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C440" t="s">
+      <c r="D440" t="s">
+        <v>50</v>
+      </c>
+      <c r="E440" t="s">
+        <v>12</v>
+      </c>
+      <c r="F440" t="s">
         <v>1346</v>
       </c>
-      <c r="D440" t="s">
-        <v>11</v>
-      </c>
-      <c r="E440" t="s">
-        <v>12</v>
-      </c>
-      <c r="F440" t="s">
-        <v>1347</v>
-      </c>
       <c r="G440" t="s">
         <v>14</v>
       </c>
       <c r="H440">
-        <v>196</v>
+        <v>100</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C441" t="s">
         <v>1348</v>
       </c>
-      <c r="B441" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C441" t="s">
+      <c r="D441" t="s">
+        <v>50</v>
+      </c>
+      <c r="E441" t="s">
+        <v>12</v>
+      </c>
+      <c r="F441" t="s">
         <v>1349</v>
       </c>
-      <c r="D441" t="s">
-        <v>11</v>
-      </c>
-      <c r="E441" t="s">
-        <v>12</v>
-      </c>
-      <c r="F441" t="s">
-        <v>1350</v>
-      </c>
       <c r="G441" t="s">
         <v>14</v>
       </c>
       <c r="H441">
-        <v>118</v>
+        <v>256</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B442" t="s">
         <v>1351</v>
-      </c>
-      <c r="B442" t="s">
-        <v>1339</v>
       </c>
       <c r="C442" t="s">
         <v>1352</v>
@@ -16552,7 +16588,7 @@
         <v>14</v>
       </c>
       <c r="H442">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.25">
@@ -16560,7 +16596,7 @@
         <v>1354</v>
       </c>
       <c r="B443" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C443" t="s">
         <v>1355</v>
@@ -16578,7 +16614,7 @@
         <v>14</v>
       </c>
       <c r="H443">
-        <v>261</v>
+        <v>95</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.25">
@@ -16586,13 +16622,13 @@
         <v>1357</v>
       </c>
       <c r="B444" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C444" t="s">
         <v>1358</v>
       </c>
       <c r="D444" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E444" t="s">
         <v>12</v>
@@ -16604,7 +16640,7 @@
         <v>14</v>
       </c>
       <c r="H444">
-        <v>105</v>
+        <v>231</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.25">
@@ -16612,13 +16648,13 @@
         <v>1360</v>
       </c>
       <c r="B445" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C445" t="s">
         <v>1361</v>
       </c>
       <c r="D445" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E445" t="s">
         <v>12</v>
@@ -16630,7 +16666,7 @@
         <v>14</v>
       </c>
       <c r="H445">
-        <v>158</v>
+        <v>248</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.25">
@@ -16638,13 +16674,13 @@
         <v>1363</v>
       </c>
       <c r="B446" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C446" t="s">
         <v>1364</v>
       </c>
       <c r="D446" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E446" t="s">
         <v>12</v>
@@ -16656,7 +16692,7 @@
         <v>14</v>
       </c>
       <c r="H446">
-        <v>138</v>
+        <v>158</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.25">
@@ -16664,13 +16700,13 @@
         <v>1366</v>
       </c>
       <c r="B447" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C447" t="s">
         <v>1367</v>
       </c>
       <c r="D447" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E447" t="s">
         <v>12</v>
@@ -16682,7 +16718,7 @@
         <v>14</v>
       </c>
       <c r="H447">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.25">
@@ -16690,7 +16726,7 @@
         <v>1369</v>
       </c>
       <c r="B448" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C448" t="s">
         <v>1370</v>
@@ -16708,7 +16744,7 @@
         <v>14</v>
       </c>
       <c r="H448">
-        <v>185</v>
+        <v>141</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
@@ -16716,7 +16752,7 @@
         <v>1372</v>
       </c>
       <c r="B449" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C449" t="s">
         <v>1373</v>
@@ -16734,7 +16770,7 @@
         <v>14</v>
       </c>
       <c r="H449">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
@@ -16742,7 +16778,7 @@
         <v>1375</v>
       </c>
       <c r="B450" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C450" t="s">
         <v>1376</v>
@@ -16760,7 +16796,7 @@
         <v>14</v>
       </c>
       <c r="H450">
-        <v>186</v>
+        <v>106</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
@@ -16768,7 +16804,7 @@
         <v>1378</v>
       </c>
       <c r="B451" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C451" t="s">
         <v>1379</v>
@@ -16786,7 +16822,7 @@
         <v>14</v>
       </c>
       <c r="H451">
-        <v>105</v>
+        <v>269</v>
       </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
@@ -16794,7 +16830,7 @@
         <v>1381</v>
       </c>
       <c r="B452" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C452" t="s">
         <v>1382</v>
@@ -16812,7 +16848,7 @@
         <v>14</v>
       </c>
       <c r="H452">
-        <v>260</v>
+        <v>135</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
@@ -16820,7 +16856,7 @@
         <v>1384</v>
       </c>
       <c r="B453" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C453" t="s">
         <v>1385</v>
@@ -16838,7 +16874,7 @@
         <v>14</v>
       </c>
       <c r="H453">
-        <v>104</v>
+        <v>196</v>
       </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
@@ -16846,7 +16882,7 @@
         <v>1387</v>
       </c>
       <c r="B454" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C454" t="s">
         <v>1388</v>
@@ -16864,7 +16900,7 @@
         <v>14</v>
       </c>
       <c r="H454">
-        <v>209</v>
+        <v>122</v>
       </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
@@ -16872,7 +16908,7 @@
         <v>1390</v>
       </c>
       <c r="B455" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C455" t="s">
         <v>1391</v>
@@ -16890,7 +16926,7 @@
         <v>14</v>
       </c>
       <c r="H455">
-        <v>249</v>
+        <v>122</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
@@ -16898,7 +16934,7 @@
         <v>1393</v>
       </c>
       <c r="B456" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C456" t="s">
         <v>1394</v>
@@ -16916,7 +16952,7 @@
         <v>14</v>
       </c>
       <c r="H456">
-        <v>241</v>
+        <v>137</v>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
@@ -16924,7 +16960,7 @@
         <v>1396</v>
       </c>
       <c r="B457" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C457" t="s">
         <v>1397</v>
@@ -16942,7 +16978,7 @@
         <v>14</v>
       </c>
       <c r="H457">
-        <v>143</v>
+        <v>220</v>
       </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
@@ -16950,111 +16986,111 @@
         <v>1399</v>
       </c>
       <c r="B458" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C458" t="s">
         <v>1400</v>
       </c>
-      <c r="C458" t="s">
+      <c r="D458" t="s">
+        <v>50</v>
+      </c>
+      <c r="E458" t="s">
+        <v>12</v>
+      </c>
+      <c r="F458" t="s">
         <v>1401</v>
       </c>
-      <c r="D458" t="s">
-        <v>11</v>
-      </c>
-      <c r="E458" t="s">
-        <v>12</v>
-      </c>
-      <c r="F458" t="s">
-        <v>1402</v>
-      </c>
       <c r="G458" t="s">
         <v>14</v>
       </c>
       <c r="H458">
-        <v>234</v>
+        <v>187</v>
       </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C459" t="s">
         <v>1403</v>
       </c>
-      <c r="B459" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C459" t="s">
+      <c r="D459" t="s">
+        <v>50</v>
+      </c>
+      <c r="E459" t="s">
+        <v>12</v>
+      </c>
+      <c r="F459" t="s">
         <v>1404</v>
       </c>
-      <c r="D459" t="s">
-        <v>11</v>
-      </c>
-      <c r="E459" t="s">
-        <v>12</v>
-      </c>
-      <c r="F459" t="s">
-        <v>1405</v>
-      </c>
       <c r="G459" t="s">
         <v>14</v>
       </c>
       <c r="H459">
-        <v>244</v>
+        <v>196</v>
       </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C460" t="s">
         <v>1406</v>
       </c>
-      <c r="B460" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C460" t="s">
+      <c r="D460" t="s">
+        <v>50</v>
+      </c>
+      <c r="E460" t="s">
+        <v>12</v>
+      </c>
+      <c r="F460" t="s">
         <v>1407</v>
       </c>
-      <c r="D460" t="s">
-        <v>11</v>
-      </c>
-      <c r="E460" t="s">
-        <v>12</v>
-      </c>
-      <c r="F460" t="s">
-        <v>1408</v>
-      </c>
       <c r="G460" t="s">
         <v>14</v>
       </c>
       <c r="H460">
-        <v>198</v>
+        <v>219</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C461" t="s">
         <v>1409</v>
       </c>
-      <c r="B461" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C461" t="s">
+      <c r="D461" t="s">
+        <v>50</v>
+      </c>
+      <c r="E461" t="s">
+        <v>12</v>
+      </c>
+      <c r="F461" t="s">
         <v>1410</v>
       </c>
-      <c r="D461" t="s">
-        <v>11</v>
-      </c>
-      <c r="E461" t="s">
-        <v>12</v>
-      </c>
-      <c r="F461" t="s">
-        <v>1411</v>
-      </c>
       <c r="G461" t="s">
         <v>14</v>
       </c>
       <c r="H461">
-        <v>123</v>
+        <v>258</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B462" t="s">
         <v>1412</v>
-      </c>
-      <c r="B462" t="s">
-        <v>1400</v>
       </c>
       <c r="C462" t="s">
         <v>1413</v>
@@ -17072,7 +17108,7 @@
         <v>14</v>
       </c>
       <c r="H462">
-        <v>165</v>
+        <v>235</v>
       </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
@@ -17080,7 +17116,7 @@
         <v>1415</v>
       </c>
       <c r="B463" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C463" t="s">
         <v>1416</v>
@@ -17098,7 +17134,7 @@
         <v>14</v>
       </c>
       <c r="H463">
-        <v>131</v>
+        <v>204</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
@@ -17106,7 +17142,7 @@
         <v>1418</v>
       </c>
       <c r="B464" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C464" t="s">
         <v>1419</v>
@@ -17124,7 +17160,7 @@
         <v>14</v>
       </c>
       <c r="H464">
-        <v>235</v>
+        <v>153</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
@@ -17132,7 +17168,7 @@
         <v>1421</v>
       </c>
       <c r="B465" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C465" t="s">
         <v>1422</v>
@@ -17150,7 +17186,7 @@
         <v>14</v>
       </c>
       <c r="H465">
-        <v>175</v>
+        <v>249</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
@@ -17158,7 +17194,7 @@
         <v>1424</v>
       </c>
       <c r="B466" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C466" t="s">
         <v>1425</v>
@@ -17176,7 +17212,7 @@
         <v>14</v>
       </c>
       <c r="H466">
-        <v>172</v>
+        <v>104</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
@@ -17184,7 +17220,7 @@
         <v>1427</v>
       </c>
       <c r="B467" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C467" t="s">
         <v>1428</v>
@@ -17202,7 +17238,7 @@
         <v>14</v>
       </c>
       <c r="H467">
-        <v>147</v>
+        <v>259</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
@@ -17210,7 +17246,7 @@
         <v>1430</v>
       </c>
       <c r="B468" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C468" t="s">
         <v>1431</v>
@@ -17228,7 +17264,7 @@
         <v>14</v>
       </c>
       <c r="H468">
-        <v>266</v>
+        <v>253</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
@@ -17236,7 +17272,7 @@
         <v>1433</v>
       </c>
       <c r="B469" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C469" t="s">
         <v>1434</v>
@@ -17254,7 +17290,7 @@
         <v>14</v>
       </c>
       <c r="H469">
-        <v>199</v>
+        <v>112</v>
       </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
@@ -17262,7 +17298,7 @@
         <v>1436</v>
       </c>
       <c r="B470" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C470" t="s">
         <v>1437</v>
@@ -17280,7 +17316,7 @@
         <v>14</v>
       </c>
       <c r="H470">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
@@ -17288,7 +17324,7 @@
         <v>1439</v>
       </c>
       <c r="B471" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C471" t="s">
         <v>1440</v>
@@ -17306,7 +17342,7 @@
         <v>14</v>
       </c>
       <c r="H471">
-        <v>233</v>
+        <v>143</v>
       </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
@@ -17314,7 +17350,7 @@
         <v>1442</v>
       </c>
       <c r="B472" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C472" t="s">
         <v>1443</v>
@@ -17332,7 +17368,7 @@
         <v>14</v>
       </c>
       <c r="H472">
-        <v>99</v>
+        <v>257</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
@@ -17340,13 +17376,13 @@
         <v>1445</v>
       </c>
       <c r="B473" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C473" t="s">
         <v>1446</v>
       </c>
       <c r="D473" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E473" t="s">
         <v>12</v>
@@ -17358,7 +17394,7 @@
         <v>14</v>
       </c>
       <c r="H473">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
@@ -17366,13 +17402,13 @@
         <v>1448</v>
       </c>
       <c r="B474" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C474" t="s">
         <v>1449</v>
       </c>
       <c r="D474" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E474" t="s">
         <v>12</v>
@@ -17384,7 +17420,7 @@
         <v>14</v>
       </c>
       <c r="H474">
-        <v>222</v>
+        <v>138</v>
       </c>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.25">
@@ -17392,13 +17428,13 @@
         <v>1451</v>
       </c>
       <c r="B475" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C475" t="s">
         <v>1452</v>
       </c>
       <c r="D475" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E475" t="s">
         <v>12</v>
@@ -17410,7 +17446,7 @@
         <v>14</v>
       </c>
       <c r="H475">
-        <v>170</v>
+        <v>218</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
@@ -17418,13 +17454,13 @@
         <v>1454</v>
       </c>
       <c r="B476" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C476" t="s">
         <v>1455</v>
       </c>
       <c r="D476" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E476" t="s">
         <v>12</v>
@@ -17436,7 +17472,7 @@
         <v>14</v>
       </c>
       <c r="H476">
-        <v>225</v>
+        <v>184</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
@@ -17444,7 +17480,7 @@
         <v>1457</v>
       </c>
       <c r="B477" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C477" t="s">
         <v>1458</v>
@@ -17462,7 +17498,7 @@
         <v>14</v>
       </c>
       <c r="H477">
-        <v>112</v>
+        <v>153</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
@@ -17470,7 +17506,7 @@
         <v>1460</v>
       </c>
       <c r="B478" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C478" t="s">
         <v>1461</v>
@@ -17488,7 +17524,7 @@
         <v>14</v>
       </c>
       <c r="H478">
-        <v>247</v>
+        <v>127</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
@@ -17496,7 +17532,7 @@
         <v>1463</v>
       </c>
       <c r="B479" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C479" t="s">
         <v>1464</v>
@@ -17514,7 +17550,7 @@
         <v>14</v>
       </c>
       <c r="H479">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -17522,7 +17558,7 @@
         <v>1466</v>
       </c>
       <c r="B480" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C480" t="s">
         <v>1467</v>
@@ -17540,7 +17576,7 @@
         <v>14</v>
       </c>
       <c r="H480">
-        <v>258</v>
+        <v>205</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
@@ -17548,7 +17584,7 @@
         <v>1469</v>
       </c>
       <c r="B481" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C481" t="s">
         <v>1470</v>
@@ -17566,7 +17602,7 @@
         <v>14</v>
       </c>
       <c r="H481">
-        <v>195</v>
+        <v>237</v>
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
@@ -17574,7 +17610,7 @@
         <v>1472</v>
       </c>
       <c r="B482" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C482" t="s">
         <v>1473</v>
@@ -17592,7 +17628,7 @@
         <v>14</v>
       </c>
       <c r="H482">
-        <v>90</v>
+        <v>262</v>
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
@@ -17600,7 +17636,7 @@
         <v>1475</v>
       </c>
       <c r="B483" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C483" t="s">
         <v>1476</v>
@@ -17618,7 +17654,7 @@
         <v>14</v>
       </c>
       <c r="H483">
-        <v>133</v>
+        <v>91</v>
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
@@ -17626,7 +17662,7 @@
         <v>1478</v>
       </c>
       <c r="B484" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C484" t="s">
         <v>1479</v>
@@ -17644,7 +17680,7 @@
         <v>14</v>
       </c>
       <c r="H484">
-        <v>148</v>
+        <v>126</v>
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
@@ -17652,7 +17688,7 @@
         <v>1481</v>
       </c>
       <c r="B485" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C485" t="s">
         <v>1482</v>
@@ -17670,7 +17706,7 @@
         <v>14</v>
       </c>
       <c r="H485">
-        <v>162</v>
+        <v>196</v>
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
@@ -17678,7 +17714,7 @@
         <v>1484</v>
       </c>
       <c r="B486" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C486" t="s">
         <v>1485</v>
@@ -17696,7 +17732,7 @@
         <v>14</v>
       </c>
       <c r="H486">
-        <v>202</v>
+        <v>233</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
@@ -17704,7 +17740,7 @@
         <v>1487</v>
       </c>
       <c r="B487" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C487" t="s">
         <v>1488</v>
@@ -17722,7 +17758,7 @@
         <v>14</v>
       </c>
       <c r="H487">
-        <v>100</v>
+        <v>246</v>
       </c>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
@@ -17730,7 +17766,7 @@
         <v>1490</v>
       </c>
       <c r="B488" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C488" t="s">
         <v>1491</v>
@@ -17748,7 +17784,7 @@
         <v>14</v>
       </c>
       <c r="H488">
-        <v>216</v>
+        <v>101</v>
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
@@ -17756,7 +17792,7 @@
         <v>1493</v>
       </c>
       <c r="B489" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C489" t="s">
         <v>1494</v>
@@ -17774,7 +17810,7 @@
         <v>14</v>
       </c>
       <c r="H489">
-        <v>224</v>
+        <v>119</v>
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
@@ -17782,7 +17818,7 @@
         <v>1496</v>
       </c>
       <c r="B490" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C490" t="s">
         <v>1497</v>
@@ -17800,7 +17836,7 @@
         <v>14</v>
       </c>
       <c r="H490">
-        <v>179</v>
+        <v>231</v>
       </c>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
@@ -17808,7 +17844,7 @@
         <v>1499</v>
       </c>
       <c r="B491" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C491" t="s">
         <v>1500</v>
@@ -17826,7 +17862,7 @@
         <v>14</v>
       </c>
       <c r="H491">
-        <v>117</v>
+        <v>222</v>
       </c>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
@@ -17834,7 +17870,7 @@
         <v>1502</v>
       </c>
       <c r="B492" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C492" t="s">
         <v>1503</v>
@@ -17852,7 +17888,7 @@
         <v>14</v>
       </c>
       <c r="H492">
-        <v>179</v>
+        <v>268</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
@@ -17860,7 +17896,7 @@
         <v>1505</v>
       </c>
       <c r="B493" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C493" t="s">
         <v>1506</v>
@@ -17878,7 +17914,7 @@
         <v>14</v>
       </c>
       <c r="H493">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
@@ -17886,7 +17922,7 @@
         <v>1508</v>
       </c>
       <c r="B494" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C494" t="s">
         <v>1509</v>
@@ -17904,7 +17940,7 @@
         <v>14</v>
       </c>
       <c r="H494">
-        <v>194</v>
+        <v>163</v>
       </c>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
@@ -17912,7 +17948,7 @@
         <v>1511</v>
       </c>
       <c r="B495" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C495" t="s">
         <v>1512</v>
@@ -17930,7 +17966,7 @@
         <v>14</v>
       </c>
       <c r="H495">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
@@ -17938,7 +17974,7 @@
         <v>1514</v>
       </c>
       <c r="B496" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C496" t="s">
         <v>1515</v>
@@ -17956,7 +17992,7 @@
         <v>14</v>
       </c>
       <c r="H496">
-        <v>214</v>
+        <v>167</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
@@ -17964,7 +18000,7 @@
         <v>1517</v>
       </c>
       <c r="B497" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C497" t="s">
         <v>1518</v>
@@ -17982,7 +18018,7 @@
         <v>14</v>
       </c>
       <c r="H497">
-        <v>119</v>
+        <v>145</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
@@ -17990,7 +18026,7 @@
         <v>1520</v>
       </c>
       <c r="B498" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C498" t="s">
         <v>1521</v>
@@ -18008,7 +18044,7 @@
         <v>14</v>
       </c>
       <c r="H498">
-        <v>214</v>
+        <v>98</v>
       </c>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
@@ -18016,7 +18052,7 @@
         <v>1523</v>
       </c>
       <c r="B499" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C499" t="s">
         <v>1524</v>
@@ -18034,7 +18070,7 @@
         <v>14</v>
       </c>
       <c r="H499">
-        <v>245</v>
+        <v>138</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
@@ -18042,7 +18078,7 @@
         <v>1526</v>
       </c>
       <c r="B500" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C500" t="s">
         <v>1527</v>
@@ -18060,7 +18096,7 @@
         <v>14</v>
       </c>
       <c r="H500">
-        <v>190</v>
+        <v>268</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
@@ -18068,7 +18104,7 @@
         <v>1529</v>
       </c>
       <c r="B501" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C501" t="s">
         <v>1530</v>
@@ -18086,7 +18122,7 @@
         <v>14</v>
       </c>
       <c r="H501">
-        <v>149</v>
+        <v>117</v>
       </c>
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
@@ -18094,7 +18130,7 @@
         <v>1532</v>
       </c>
       <c r="B502" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C502" t="s">
         <v>1533</v>
@@ -18112,7 +18148,7 @@
         <v>14</v>
       </c>
       <c r="H502">
-        <v>185</v>
+        <v>112</v>
       </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
@@ -18120,7 +18156,7 @@
         <v>1535</v>
       </c>
       <c r="B503" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C503" t="s">
         <v>1536</v>
@@ -18138,7 +18174,7 @@
         <v>14</v>
       </c>
       <c r="H503">
-        <v>123</v>
+        <v>253</v>
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
@@ -18146,7 +18182,7 @@
         <v>1538</v>
       </c>
       <c r="B504" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C504" t="s">
         <v>1539</v>
@@ -18164,7 +18200,7 @@
         <v>14</v>
       </c>
       <c r="H504">
-        <v>142</v>
+        <v>162</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -18172,7 +18208,7 @@
         <v>1541</v>
       </c>
       <c r="B505" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C505" t="s">
         <v>1542</v>
@@ -18190,7 +18226,7 @@
         <v>14</v>
       </c>
       <c r="H505">
-        <v>178</v>
+        <v>235</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -18198,7 +18234,7 @@
         <v>1544</v>
       </c>
       <c r="B506" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C506" t="s">
         <v>1545</v>
@@ -18216,7 +18252,7 @@
         <v>14</v>
       </c>
       <c r="H506">
-        <v>168</v>
+        <v>228</v>
       </c>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
@@ -18224,7 +18260,7 @@
         <v>1547</v>
       </c>
       <c r="B507" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C507" t="s">
         <v>1548</v>
@@ -18242,7 +18278,111 @@
         <v>14</v>
       </c>
       <c r="H507">
-        <v>162</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D508" t="s">
+        <v>50</v>
+      </c>
+      <c r="E508" t="s">
+        <v>12</v>
+      </c>
+      <c r="F508" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G508" t="s">
+        <v>14</v>
+      </c>
+      <c r="H508">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D509" t="s">
+        <v>50</v>
+      </c>
+      <c r="E509" t="s">
+        <v>12</v>
+      </c>
+      <c r="F509" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G509" t="s">
+        <v>14</v>
+      </c>
+      <c r="H509">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D510" t="s">
+        <v>50</v>
+      </c>
+      <c r="E510" t="s">
+        <v>12</v>
+      </c>
+      <c r="F510" t="s">
+        <v>1558</v>
+      </c>
+      <c r="G510" t="s">
+        <v>14</v>
+      </c>
+      <c r="H510">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D511" t="s">
+        <v>50</v>
+      </c>
+      <c r="E511" t="s">
+        <v>12</v>
+      </c>
+      <c r="F511" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G511" t="s">
+        <v>14</v>
+      </c>
+      <c r="H511">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
